--- a/data/ECOGR (TRY).xlsx
+++ b/data/ECOGR (TRY).xlsx
@@ -12,6 +12,28 @@
     <sheet name="Nakit Akış (Yıllıklan.)" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -381,14 +403,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:G108"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -396,18 +419,21 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -421,29 +447,29 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>980613670</v>
+        <v>1590644550</v>
       </c>
       <c r="C3">
-        <v>1123380595.4479482</v>
+        <v>1023321599.5993431</v>
       </c>
       <c r="D3">
-        <v>412447813</v>
+        <v>1172306345.5689507</v>
       </c>
       <c r="E3">
-        <v>192527613.09631342</v>
+        <v>430410842</v>
       </c>
       <c r="F3">
-        <v>676334534.8200129</v>
+        <v>200912623.4195398</v>
+      </c>
+      <c r="G3">
+        <v>705790424.1089084</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v xml:space="preserve">    Gayrimenkul Projeleri Kapsamında Açılan Nakit Hesapları</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="D4">
+      <c r="C4">
         <v>0</v>
       </c>
     </row>
@@ -458,23 +484,23 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>50197931</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>697009202.4074364</v>
+        <v>52384164</v>
       </c>
       <c r="F5">
-        <v>282665300.7150187</v>
+        <v>727365519.9432821</v>
+      </c>
+      <c r="G5">
+        <v>294976009.9498942</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Teminata Verilen Finansal Varlıklar</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="D6">
+      <c r="C6">
         <v>0</v>
       </c>
     </row>
@@ -483,29 +509,29 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>555467782</v>
+        <v>1385664812</v>
       </c>
       <c r="C7">
-        <v>952592809.8056427</v>
+        <v>579659652.5134503</v>
       </c>
       <c r="D7">
-        <v>477459991</v>
+        <v>994080367.9568765</v>
       </c>
       <c r="E7">
-        <v>354158567.8754474</v>
+        <v>498254447</v>
       </c>
       <c r="F7">
-        <v>169909259.83304226</v>
+        <v>369582969.60118383</v>
+      </c>
+      <c r="G7">
+        <v>177309190.0290246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="D8">
+      <c r="C8">
         <v>0</v>
       </c>
     </row>
@@ -513,10 +539,7 @@
       <c r="A9" t="str">
         <v xml:space="preserve">    Türkiye Cumhuriyet Merkez Bankası Hesabı</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="D9">
+      <c r="C9">
         <v>0</v>
       </c>
     </row>
@@ -525,29 +548,29 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>7868545</v>
+        <v>9312789</v>
       </c>
       <c r="C10">
-        <v>6206240.870272048</v>
+        <v>8211237.82204608</v>
       </c>
       <c r="D10">
-        <v>367603</v>
+        <v>6476536.61086084</v>
       </c>
       <c r="E10">
-        <v>847820.407691792</v>
+        <v>383613</v>
       </c>
       <c r="F10">
-        <v>1157912.4972399327</v>
+        <v>884744.892218494</v>
+      </c>
+      <c r="G10">
+        <v>1208342.1893064552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="D11">
+      <c r="C11">
         <v>0</v>
       </c>
     </row>
@@ -555,10 +578,7 @@
       <c r="A12" t="str">
         <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="D12">
+      <c r="C12">
         <v>0</v>
       </c>
     </row>
@@ -573,12 +593,15 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>701141</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>373918.5161533378</v>
+        <v>731677</v>
       </c>
       <c r="F13">
+        <v>390203.50804394396</v>
+      </c>
+      <c r="G13">
         <v>0</v>
       </c>
     </row>
@@ -587,29 +610,29 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
-        <v>150552841</v>
+        <v>160725129</v>
       </c>
       <c r="C14">
-        <v>108884769.38652116</v>
+        <v>157109755.64550877</v>
       </c>
       <c r="D14">
-        <v>88181510</v>
+        <v>113626945.84975591</v>
       </c>
       <c r="E14">
-        <v>164732647.55607775</v>
+        <v>92022013</v>
       </c>
       <c r="F14">
-        <v>257735501.1107443</v>
+        <v>171907124.65115878</v>
+      </c>
+      <c r="G14">
+        <v>268960461.53444415</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v xml:space="preserve">    Proje Halindeki Stoklar</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="D15">
+      <c r="C15">
         <v>0</v>
       </c>
     </row>
@@ -617,10 +640,7 @@
       <c r="A16" t="str">
         <v xml:space="preserve">    Canlı Varlıklar</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="D16">
+      <c r="C16">
         <v>0</v>
       </c>
     </row>
@@ -629,29 +649,29 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>781833234</v>
+        <v>1066245595</v>
       </c>
       <c r="C17">
-        <v>929677237.0275177</v>
+        <v>815883828.7832633</v>
       </c>
       <c r="D17">
-        <v>725542316</v>
+        <v>970166770.4735311</v>
       </c>
       <c r="E17">
-        <v>311896617.25182223</v>
+        <v>757141315</v>
       </c>
       <c r="F17">
-        <v>1904900337.3830028</v>
+        <v>325480416.02944285</v>
+      </c>
+      <c r="G17">
+        <v>1987863029.0031574</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v xml:space="preserve">    Ertelenmiş Sigortacılık Üretim Giderleri</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="D18">
+      <c r="C18">
         <v>0</v>
       </c>
     </row>
@@ -660,29 +680,29 @@
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
       <c r="B19">
-        <v>14772135</v>
+        <v>25426264</v>
       </c>
       <c r="C19">
-        <v>10080791.24937663</v>
+        <v>15415494.684769632</v>
       </c>
       <c r="D19">
-        <v>4780853</v>
+        <v>10519832.368377196</v>
       </c>
       <c r="E19">
-        <v>245388.42718626384</v>
+        <v>4989070</v>
       </c>
       <c r="F19">
-        <v>7914545.701848878</v>
+        <v>256075.64478620252</v>
+      </c>
+      <c r="G19">
+        <v>8259241.957863078</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v xml:space="preserve">    Nakit Dışı Serbest Kullanılabilir Teminatlar</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="D20">
+      <c r="C20">
         <v>0</v>
       </c>
     </row>
@@ -691,29 +711,29 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>75144929</v>
+        <v>41270795</v>
       </c>
       <c r="C21">
-        <v>128940918.03772464</v>
+        <v>78417659.57235642</v>
       </c>
       <c r="D21">
-        <v>134958762</v>
+        <v>134556584.85790044</v>
       </c>
       <c r="E21">
-        <v>320736047.8775609</v>
+        <v>140836519</v>
       </c>
       <c r="F21">
-        <v>252669368.9370181</v>
+        <v>334704823.7286322</v>
+      </c>
+      <c r="G21">
+        <v>263673687.9166552</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlıklar</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="D22">
+      <c r="C22">
         <v>0</v>
       </c>
     </row>
@@ -721,10 +741,7 @@
       <c r="A23" t="str">
         <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıklar</v>
       </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="D23">
+      <c r="C23">
         <v>0</v>
       </c>
     </row>
@@ -733,19 +750,22 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>2566253136</v>
+        <v>4279289934</v>
       </c>
       <c r="C24">
-        <v>3259763361.825003</v>
+        <v>2678019228.6207376</v>
       </c>
       <c r="D24">
-        <v>1894637920</v>
+        <v>3401733383.6862526</v>
       </c>
       <c r="E24">
-        <v>2042527823.4156895</v>
+        <v>1977153660</v>
       </c>
       <c r="F24">
-        <v>3553286760.997928</v>
+        <v>2131484501.4182882</v>
+      </c>
+      <c r="G24">
+        <v>3708040386.689254</v>
       </c>
     </row>
     <row r="25">
@@ -757,10 +777,7 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="D26">
+      <c r="C26">
         <v>0</v>
       </c>
     </row>
@@ -768,10 +785,7 @@
       <c r="A27" t="str">
         <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve Bağlı Ortaklıklardaki Yatırımlar</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-      <c r="D27">
+      <c r="C27">
         <v>0</v>
       </c>
     </row>
@@ -780,18 +794,21 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>560155</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>42971523</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>28295954.23584927</v>
+        <v>44843029</v>
       </c>
       <c r="F28">
+        <v>29528306.647835206</v>
+      </c>
+      <c r="G28">
         <v>0</v>
       </c>
     </row>
@@ -799,10 +816,7 @@
       <c r="A29" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklar</v>
       </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="D29">
+      <c r="C29">
         <v>0</v>
       </c>
     </row>
@@ -811,29 +825,29 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B30">
-        <v>6492014</v>
+        <v>66811691</v>
       </c>
       <c r="C30">
-        <v>6999162.015235444</v>
+        <v>6774755.80276311</v>
       </c>
       <c r="D30">
-        <v>6945030</v>
+        <v>7303991.254053898</v>
       </c>
       <c r="E30">
-        <v>12722529.75329564</v>
+        <v>7247502</v>
       </c>
       <c r="F30">
-        <v>9434379.226216968</v>
+        <v>13276624.522369476</v>
+      </c>
+      <c r="G30">
+        <v>9845267.648572715</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklar</v>
       </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="D31">
+      <c r="C31">
         <v>0</v>
       </c>
     </row>
@@ -841,10 +855,7 @@
       <c r="A32" t="str">
         <v xml:space="preserve">    İmtiyaz Sözleşmelerine İlişkin Finansal Varlıklar</v>
       </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="D32">
+      <c r="C32">
         <v>0</v>
       </c>
     </row>
@@ -852,10 +863,7 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Türev Araçlar</v>
       </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="D33">
+      <c r="C33">
         <v>0</v>
       </c>
     </row>
@@ -863,10 +871,7 @@
       <c r="A34" t="str">
         <v xml:space="preserve">    Stoklar</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="D34">
+      <c r="C34">
         <v>0</v>
       </c>
     </row>
@@ -875,20 +880,20 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlar</v>
       </c>
       <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>9216</v>
+        <v>33300</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>9617</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v xml:space="preserve">    Canlı Varlıklar</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="D36">
+      <c r="C36">
         <v>0</v>
       </c>
     </row>
@@ -903,12 +908,15 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>13093555</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>36925005.23638245</v>
+        <v>13663809</v>
       </c>
       <c r="F37">
+        <v>38533172.21623986</v>
+      </c>
+      <c r="G37">
         <v>0</v>
       </c>
     </row>
@@ -916,10 +924,7 @@
       <c r="A38" t="str">
         <v xml:space="preserve">    Proje Halindeki Yatırım Amaçlı Gayrimenkuller</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="D38">
+      <c r="C38">
         <v>0</v>
       </c>
     </row>
@@ -928,19 +933,22 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>27826885795</v>
+        <v>28933865288</v>
       </c>
       <c r="C39">
-        <v>27940637684.52369</v>
+        <v>29038809221.99222</v>
       </c>
       <c r="D39">
-        <v>28387403154</v>
+        <v>29157515262.001667</v>
       </c>
       <c r="E39">
-        <v>31441043213.1244</v>
+        <v>29623738372</v>
       </c>
       <c r="F39">
-        <v>15933624699.940502</v>
+        <v>32810371319.753815</v>
+      </c>
+      <c r="G39">
+        <v>16627569871.995275</v>
       </c>
     </row>
     <row r="40">
@@ -948,19 +956,22 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
-        <v>6909092</v>
+        <v>5229210</v>
       </c>
       <c r="C40">
-        <v>6535884.781764719</v>
+        <v>7209998.487191214</v>
       </c>
       <c r="D40">
-        <v>4554140</v>
+        <v>6820537.255688548</v>
       </c>
       <c r="E40">
-        <v>9707044.740234407</v>
+        <v>4752483</v>
       </c>
       <c r="F40">
-        <v>1971703.4678705179</v>
+        <v>10129808.358636346</v>
+      </c>
+      <c r="G40">
+        <v>2057575.585986712</v>
       </c>
     </row>
     <row r="41">
@@ -968,19 +979,22 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>33697815</v>
+        <v>34946844</v>
       </c>
       <c r="C41">
-        <v>34425368.17460738</v>
+        <v>35165430.590828635</v>
       </c>
       <c r="D41">
-        <v>34949597</v>
+        <v>35924670.34161939</v>
       </c>
       <c r="E41">
-        <v>34135025.71506655</v>
+        <v>36471730</v>
       </c>
       <c r="F41">
-        <v>22850244.515304085</v>
+        <v>35621682.81531973</v>
+      </c>
+      <c r="G41">
+        <v>23845424.027830545</v>
       </c>
     </row>
     <row r="42">
@@ -988,19 +1002,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B42">
-        <v>209817559</v>
+        <v>277735676</v>
       </c>
       <c r="C42">
-        <v>221937638.4674012</v>
+        <v>218955585.3325087</v>
       </c>
       <c r="D42">
-        <v>375198727</v>
+        <v>231603521.50481614</v>
       </c>
       <c r="E42">
-        <v>241987232.5764374</v>
+        <v>391539475</v>
       </c>
       <c r="F42">
-        <v>141174529.6874116</v>
+        <v>252526320.5057484</v>
+      </c>
+      <c r="G42">
+        <v>147322997.79423532</v>
       </c>
     </row>
     <row r="43">
@@ -1008,19 +1025,22 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Varlığı</v>
       </c>
       <c r="B43">
-        <v>300867518</v>
+        <v>316889758</v>
       </c>
       <c r="C43">
-        <v>300867518.02381736</v>
+        <v>313970974.7134609</v>
       </c>
       <c r="D43">
-        <v>300867517</v>
+        <v>313970974.7383156</v>
       </c>
       <c r="E43">
-        <v>1173821696.6088815</v>
+        <v>313970974</v>
       </c>
       <c r="F43">
-        <v>1009419429.3693126</v>
+        <v>1224944270.0693896</v>
+      </c>
+      <c r="G43">
+        <v>1053381914.5401686</v>
       </c>
     </row>
     <row r="44">
@@ -1030,8 +1050,11 @@
       <c r="B44">
         <v>0</v>
       </c>
-      <c r="D44">
-        <v>683468</v>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>713235</v>
       </c>
     </row>
     <row r="45">
@@ -1041,7 +1064,7 @@
       <c r="B45">
         <v>0</v>
       </c>
-      <c r="D45">
+      <c r="C45">
         <v>0</v>
       </c>
     </row>
@@ -1058,10 +1081,10 @@
       <c r="D46">
         <v>0</v>
       </c>
-      <c r="E46">
-        <v>986781.6468390924</v>
-      </c>
       <c r="F46">
+        <v>1029758.2056944546</v>
+      </c>
+      <c r="G46">
         <v>0</v>
       </c>
     </row>
@@ -1070,19 +1093,22 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>28384669793</v>
+        <v>29636071922</v>
       </c>
       <c r="C47">
-        <v>28511403255.986515</v>
+        <v>29620885966.918976</v>
       </c>
       <c r="D47">
-        <v>29166675927</v>
+        <v>29753138957.09616</v>
       </c>
       <c r="E47">
-        <v>32979624483.63739</v>
+        <v>30436950226</v>
       </c>
       <c r="F47">
-        <v>17118474986.206617</v>
+        <v>34415961263.09505</v>
+      </c>
+      <c r="G47">
+        <v>17864023051.592068</v>
       </c>
     </row>
     <row r="48">
@@ -1090,19 +1116,22 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>30950922929</v>
+        <v>33915361856</v>
       </c>
       <c r="C48">
-        <v>31771166617.811516</v>
+        <v>32298905195.53971</v>
       </c>
       <c r="D48">
-        <v>31061313847</v>
+        <v>33154872340.78241</v>
       </c>
       <c r="E48">
-        <v>35022152307.05308</v>
+        <v>32414103886</v>
       </c>
       <c r="F48">
-        <v>20671761747.204544</v>
+        <v>36547445764.513336</v>
+      </c>
+      <c r="G48">
+        <v>21572063438.281322</v>
       </c>
     </row>
     <row r="49">
@@ -1115,19 +1144,22 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>3472647095</v>
+        <v>3804391916</v>
       </c>
       <c r="C50">
-        <v>3505370356.1702013</v>
+        <v>3623888681.971374</v>
       </c>
       <c r="D50">
-        <v>3991585850</v>
+        <v>3658037114.722467</v>
       </c>
       <c r="E50">
-        <v>5574200152.220799</v>
+        <v>4165428386</v>
       </c>
       <c r="F50">
-        <v>2445796293.641571</v>
+        <v>5816969098.806761</v>
+      </c>
+      <c r="G50">
+        <v>2552316220.008882</v>
       </c>
     </row>
     <row r="51">
@@ -1135,10 +1167,13 @@
         <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
       </c>
       <c r="B51">
-        <v>27843605</v>
-      </c>
-      <c r="D51">
-        <v>10332511</v>
+        <v>110983693</v>
+      </c>
+      <c r="C51">
+        <v>29056256.585952207</v>
+      </c>
+      <c r="E51">
+        <v>10782515</v>
       </c>
     </row>
     <row r="52">
@@ -1146,29 +1181,29 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>808937833</v>
+        <v>1142005113</v>
       </c>
       <c r="C52">
-        <v>1327351282.421133</v>
+        <v>844168893.9967421</v>
       </c>
       <c r="D52">
-        <v>524154073</v>
+        <v>1385160414.4549944</v>
       </c>
       <c r="E52">
-        <v>332207828.6495433</v>
+        <v>546982161</v>
       </c>
       <c r="F52">
-        <v>124199453.39765084</v>
+        <v>346676226.34005815</v>
+      </c>
+      <c r="G52">
+        <v>129608618.77465783</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
       </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="D53">
+      <c r="C53">
         <v>0</v>
       </c>
     </row>
@@ -1177,19 +1212,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>12389504</v>
+        <v>146198</v>
       </c>
       <c r="C54">
-        <v>14230176.580926323</v>
+        <v>12929094.748926414</v>
       </c>
       <c r="D54">
-        <v>580638</v>
+        <v>14849932.758304946</v>
       </c>
       <c r="E54">
-        <v>482360.3363099704</v>
+        <v>605926</v>
       </c>
       <c r="F54">
-        <v>5920447.9961751755</v>
+        <v>503368.213229167</v>
+      </c>
+      <c r="G54">
+        <v>6178296.814678002</v>
       </c>
     </row>
     <row r="55">
@@ -1197,29 +1235,29 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>672034445</v>
+        <v>452154178</v>
       </c>
       <c r="C55">
-        <v>652701486.3971305</v>
+        <v>701303055.711284</v>
       </c>
       <c r="D55">
-        <v>951559071</v>
+        <v>681128103.3037001</v>
       </c>
       <c r="E55">
-        <v>85421002.73866999</v>
+        <v>993001608</v>
       </c>
       <c r="F55">
-        <v>31844900.718134712</v>
+        <v>89141279.42140113</v>
+      </c>
+      <c r="G55">
+        <v>33231817.72691776</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
       </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="D56">
+      <c r="C56">
         <v>0</v>
       </c>
     </row>
@@ -1227,10 +1265,7 @@
       <c r="A57" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
       </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="D57">
+      <c r="C57">
         <v>0</v>
       </c>
     </row>
@@ -1238,10 +1273,7 @@
       <c r="A58" t="str">
         <v xml:space="preserve">    Türev Araçlar</v>
       </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-      <c r="D58">
+      <c r="C58">
         <v>0</v>
       </c>
     </row>
@@ -1249,10 +1281,7 @@
       <c r="A59" t="str">
         <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
       </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-      <c r="D59">
+      <c r="C59">
         <v>0</v>
       </c>
     </row>
@@ -1261,29 +1290,29 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
-        <v>788993280</v>
+        <v>1355339526</v>
       </c>
       <c r="C60">
-        <v>827402155.256011</v>
+        <v>823355710.8812611</v>
       </c>
       <c r="D60">
-        <v>815802219</v>
+        <v>863437378.9919991</v>
       </c>
       <c r="E60">
-        <v>727848750.0967509</v>
+        <v>851332239</v>
       </c>
       <c r="F60">
-        <v>9550571.037268093</v>
+        <v>759548199.2570933</v>
+      </c>
+      <c r="G60">
+        <v>9966519.87417669</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="D61">
+      <c r="C61">
         <v>0</v>
       </c>
     </row>
@@ -1292,29 +1321,29 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>12442085</v>
+        <v>12908835</v>
       </c>
       <c r="C62">
-        <v>12870297.751411961</v>
+        <v>12983965.76967053</v>
       </c>
       <c r="D62">
-        <v>12638476</v>
+        <v>13430828.148963818</v>
       </c>
       <c r="E62">
-        <v>62824283.657221675</v>
+        <v>13188910</v>
       </c>
       <c r="F62">
-        <v>9782358.01005054</v>
+        <v>65560422.42995751</v>
+      </c>
+      <c r="G62">
+        <v>10208401.690645782</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="D63">
+      <c r="C63">
         <v>0</v>
       </c>
     </row>
@@ -1322,10 +1351,7 @@
       <c r="A64" t="str">
         <v xml:space="preserve">    Satış Amaçlı Sınıflandırılan Varlık Gruplarına İlişkin Yükümlülükler</v>
       </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="D64">
+      <c r="C64">
         <v>0</v>
       </c>
     </row>
@@ -1333,10 +1359,7 @@
       <c r="A65" t="str">
         <v xml:space="preserve">    Ortaklara Dağıtılmak Üzere Elde Tutulan Varlık Gruplarına İlişkin Yükümlülükler</v>
       </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="D65">
+      <c r="C65">
         <v>0</v>
       </c>
     </row>
@@ -1345,19 +1368,22 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>5795287847</v>
+        <v>6877929459</v>
       </c>
       <c r="C66">
-        <v>6339925754.576815</v>
+        <v>6047685659.665211</v>
       </c>
       <c r="D66">
-        <v>6306652838</v>
+        <v>6616043772.38043</v>
       </c>
       <c r="E66">
-        <v>6782984377.699295</v>
+        <v>6581321745</v>
       </c>
       <c r="F66">
-        <v>2627094024.8008504</v>
+        <v>7078398594.468499</v>
+      </c>
+      <c r="G66">
+        <v>2741509874.889958</v>
       </c>
     </row>
     <row r="67">
@@ -1370,29 +1396,29 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
-        <v>6370452184</v>
+        <v>6185668982</v>
       </c>
       <c r="C68">
-        <v>6529863119.467985</v>
+        <v>6647899696.4237795</v>
       </c>
       <c r="D68">
-        <v>5374805526</v>
+        <v>6814253336.463008</v>
       </c>
       <c r="E68">
-        <v>6835404523.802341</v>
+        <v>5608890388</v>
       </c>
       <c r="F68">
-        <v>6376048921.17975</v>
+        <v>7133101755.766874</v>
+      </c>
+      <c r="G68">
+        <v>6653740184.088325</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
         <v xml:space="preserve">    Diğer Finansal Yükümlülükler</v>
       </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="D69">
+      <c r="C69">
         <v>0</v>
       </c>
     </row>
@@ -1401,26 +1427,26 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B70">
-        <v>46340</v>
+        <v>689751</v>
       </c>
       <c r="C70">
-        <v>13522012.965733021</v>
+        <v>48358.21116529362</v>
       </c>
       <c r="D70">
-        <v>511533</v>
+        <v>14110927.025825545</v>
       </c>
       <c r="E70">
-        <v>140697.43491572936</v>
+        <v>533811</v>
+      </c>
+      <c r="F70">
+        <v>146825.1244728096</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Borçlar</v>
       </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="D71">
+      <c r="C71">
         <v>0</v>
       </c>
     </row>
@@ -1428,10 +1454,7 @@
       <c r="A72" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="D72">
+      <c r="C72">
         <v>0</v>
       </c>
     </row>
@@ -1440,23 +1463,23 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B73">
-        <v>292760</v>
+        <v>295736</v>
       </c>
       <c r="C73">
-        <v>314729.8285852939</v>
+        <v>305510.3560800898</v>
       </c>
       <c r="D73">
-        <v>367208</v>
+        <v>328437.0200851167</v>
+      </c>
+      <c r="E73">
+        <v>383201</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
       </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="D74">
+      <c r="C74">
         <v>0</v>
       </c>
     </row>
@@ -1464,10 +1487,7 @@
       <c r="A75" t="str">
         <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
       </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="D75">
+      <c r="C75">
         <v>0</v>
       </c>
     </row>
@@ -1475,10 +1495,7 @@
       <c r="A76" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımlardan Yükümlülükler</v>
       </c>
-      <c r="B76">
-        <v>0</v>
-      </c>
-      <c r="D76">
+      <c r="C76">
         <v>0</v>
       </c>
     </row>
@@ -1486,10 +1503,7 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Türev Araçlar</v>
       </c>
-      <c r="B77">
-        <v>0</v>
-      </c>
-      <c r="D77">
+      <c r="C77">
         <v>0</v>
       </c>
     </row>
@@ -1497,10 +1511,7 @@
       <c r="A78" t="str">
         <v xml:space="preserve">    Devlet Teşvik ve Yardımları</v>
       </c>
-      <c r="B78">
-        <v>0</v>
-      </c>
-      <c r="D78">
+      <c r="C78">
         <v>0</v>
       </c>
     </row>
@@ -1509,10 +1520,13 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B79">
-        <v>0</v>
-      </c>
-      <c r="D79">
-        <v>6115819</v>
+        <v>10591</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>6382177</v>
       </c>
     </row>
     <row r="80">
@@ -1520,29 +1534,29 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>10412875</v>
+        <v>12547481</v>
       </c>
       <c r="C80">
-        <v>10331457.066672627</v>
+        <v>10866379.112814132</v>
       </c>
       <c r="D80">
-        <v>9035314</v>
+        <v>10781415.245475182</v>
       </c>
       <c r="E80">
-        <v>4605561.900592879</v>
+        <v>9428822</v>
       </c>
       <c r="F80">
-        <v>2811409.444813021</v>
+        <v>4806144.473968526</v>
+      </c>
+      <c r="G80">
+        <v>2933852.6457567755</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Borçlar</v>
       </c>
-      <c r="B81">
-        <v>0</v>
-      </c>
-      <c r="D81">
+      <c r="C81">
         <v>0</v>
       </c>
     </row>
@@ -1551,29 +1565,29 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>3750307083</v>
+        <v>4080408244</v>
       </c>
       <c r="C82">
-        <v>3700370951.69183</v>
+        <v>3913641386.586326</v>
       </c>
       <c r="D82">
-        <v>4081368486</v>
+        <v>3861530424.510834</v>
       </c>
       <c r="E82">
-        <v>5904102325.790395</v>
+        <v>4259121258</v>
       </c>
       <c r="F82">
-        <v>3730566448.1542125</v>
+        <v>6161239253.605376</v>
+      </c>
+      <c r="G82">
+        <v>3893041002.719051</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
         <v xml:space="preserve">    Diğer Uzun Vadeli Yükümlülükler</v>
       </c>
-      <c r="B83">
-        <v>0</v>
-      </c>
-      <c r="D83">
+      <c r="C83">
         <v>0</v>
       </c>
     </row>
@@ -1582,19 +1596,22 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>10131511242</v>
+        <v>10279620785</v>
       </c>
       <c r="C84">
-        <v>10254402271.020807</v>
+        <v>10572761330.690166</v>
       </c>
       <c r="D84">
-        <v>9472203886</v>
+        <v>10701004540.265228</v>
       </c>
       <c r="E84">
-        <v>12744253108.928246</v>
+        <v>9884739657</v>
       </c>
       <c r="F84">
-        <v>10109426778.778776</v>
+        <v>13299293978.970692</v>
+      </c>
+      <c r="G84">
+        <v>10549715039.453133</v>
       </c>
     </row>
     <row r="85">
@@ -1607,19 +1624,22 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>15024123840</v>
+        <v>16757811612</v>
       </c>
       <c r="C86">
-        <v>15176838593.28894</v>
+        <v>15678458205.184336</v>
       </c>
       <c r="D86">
-        <v>15282457123</v>
+        <v>15837824029.25862</v>
       </c>
       <c r="E86">
-        <v>14871464992.544365</v>
+        <v>15948042484</v>
       </c>
       <c r="F86">
-        <v>7233633757.300773</v>
+        <v>15519150721.768066</v>
+      </c>
+      <c r="G86">
+        <v>7548674767.543097</v>
       </c>
     </row>
     <row r="87">
@@ -1627,7 +1647,7 @@
         <v xml:space="preserve">    Ödenmiş Sermaye</v>
       </c>
       <c r="B87">
-        <v>430000000</v>
+        <v>540000000</v>
       </c>
       <c r="C87">
         <v>430000000</v>
@@ -1639,6 +1659,9 @@
         <v>430000000</v>
       </c>
       <c r="F87">
+        <v>430000000</v>
+      </c>
+      <c r="G87">
         <v>170000000</v>
       </c>
     </row>
@@ -1647,29 +1670,29 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>1162056039</v>
+        <v>1233329837</v>
       </c>
       <c r="C88">
-        <v>1162056038.903099</v>
+        <v>1231393658.1990275</v>
       </c>
       <c r="D88">
-        <v>1162056039</v>
+        <v>1231393658.0979064</v>
       </c>
       <c r="E88">
-        <v>1162056038.903099</v>
+        <v>1231393658</v>
       </c>
       <c r="F88">
-        <v>889659697.2941571</v>
+        <v>1231393658.0979064</v>
+      </c>
+      <c r="G88">
+        <v>935810259.0656446</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
         <v xml:space="preserve">    Birleşme Denkleştirme Hesabı</v>
       </c>
-      <c r="B89">
-        <v>0</v>
-      </c>
-      <c r="D89">
+      <c r="C89">
         <v>0</v>
       </c>
     </row>
@@ -1677,10 +1700,7 @@
       <c r="A90" t="str">
         <v xml:space="preserve">    Pay Sahiplerinin İlave Sermaye Katkıları</v>
       </c>
-      <c r="B90">
-        <v>0</v>
-      </c>
-      <c r="D90">
+      <c r="C90">
         <v>0</v>
       </c>
     </row>
@@ -1688,10 +1708,7 @@
       <c r="A91" t="str">
         <v xml:space="preserve">    Sermaye Avansı</v>
       </c>
-      <c r="B91">
-        <v>0</v>
-      </c>
-      <c r="D91">
+      <c r="C91">
         <v>0</v>
       </c>
     </row>
@@ -1699,10 +1716,7 @@
       <c r="A92" t="str">
         <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
       </c>
-      <c r="B92">
-        <v>0</v>
-      </c>
-      <c r="D92">
+      <c r="C92">
         <v>0</v>
       </c>
     </row>
@@ -1710,10 +1724,7 @@
       <c r="A93" t="str">
         <v xml:space="preserve">    Karşılıklı İştirak Sermaye Düzeltmesi (-)</v>
       </c>
-      <c r="B93">
-        <v>0</v>
-      </c>
-      <c r="D93">
+      <c r="C93">
         <v>0</v>
       </c>
     </row>
@@ -1722,9 +1733,12 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>0</v>
-      </c>
-      <c r="D94">
+        <v>1006024274</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="E94">
         <v>0</v>
       </c>
     </row>
@@ -1737,10 +1751,7 @@
       <c r="A96" t="str">
         <v xml:space="preserve">    Pay Bazlı Ödemeler (-)</v>
       </c>
-      <c r="B96">
-        <v>0</v>
-      </c>
-      <c r="D96">
+      <c r="C96">
         <v>0</v>
       </c>
     </row>
@@ -1749,19 +1760,22 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>7867783359</v>
+        <v>8208821383</v>
       </c>
       <c r="C97">
-        <v>7869351827.218191</v>
+        <v>8210443009.868476</v>
       </c>
       <c r="D97">
-        <v>8184152631</v>
+        <v>8212079788.403248</v>
       </c>
       <c r="E97">
-        <v>10301166307.35227</v>
+        <v>8540590875</v>
       </c>
       <c r="F97">
-        <v>4911458769.241184</v>
+        <v>10749805255.497389</v>
+      </c>
+      <c r="G97">
+        <v>5125363838.856243</v>
       </c>
     </row>
     <row r="98">
@@ -1769,10 +1783,13 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B98">
-        <v>-1578662231</v>
-      </c>
-      <c r="D98">
-        <v>-1116691245</v>
+        <v>-1923401435</v>
+      </c>
+      <c r="C98">
+        <v>-1647416519.7533782</v>
+      </c>
+      <c r="E98">
+        <v>-1165325659</v>
       </c>
     </row>
     <row r="99">
@@ -1780,46 +1797,43 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>9245672</v>
+        <v>9648342</v>
       </c>
       <c r="C99">
-        <v>9245671.409367947</v>
+        <v>9648341.798468767</v>
       </c>
       <c r="D99">
-        <v>9245672</v>
+        <v>9648341.182113359</v>
       </c>
       <c r="E99">
-        <v>6752515.786780411</v>
+        <v>9648342</v>
+      </c>
+      <c r="F99">
+        <v>7046603.027926326</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
       <c r="C100">
-        <v>-1500293131.214404</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
-      </c>
-      <c r="E100">
-        <v>-1931508134.1834958</v>
+        <v>-1565634269.510266</v>
       </c>
       <c r="F100">
-        <v>-1321814223.0021167</v>
+        <v>-2015629655.1646047</v>
+      </c>
+      <c r="G100">
+        <v>-1379382203.65181</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
         <v xml:space="preserve">    Diğer Yedekler</v>
       </c>
-      <c r="B101">
-        <v>0</v>
-      </c>
-      <c r="D101">
+      <c r="C101">
         <v>0</v>
       </c>
     </row>
@@ -1827,10 +1841,7 @@
       <c r="A102" t="str">
         <v xml:space="preserve">    Ödenen Kar Payı Avansları (Net) (-)</v>
       </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-      <c r="D102">
+      <c r="C102">
         <v>0</v>
       </c>
     </row>
@@ -1839,19 +1850,22 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>7006530863</v>
+        <v>7311681031</v>
       </c>
       <c r="C103">
-        <v>7006530863.319316</v>
+        <v>7311681031.702654</v>
       </c>
       <c r="D103">
-        <v>5423038593</v>
+        <v>7311681032.035876</v>
       </c>
       <c r="E103">
-        <v>2701416128.9414496</v>
+        <v>5659224113</v>
       </c>
       <c r="F103">
-        <v>2434915279.549609</v>
+        <v>2819068873.730701</v>
+      </c>
+      <c r="G103">
+        <v>2540961313.2943454</v>
       </c>
     </row>
     <row r="104">
@@ -1859,19 +1873,22 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>203532016</v>
+        <v>451395788</v>
       </c>
       <c r="C104">
-        <v>199947323.6533713</v>
+        <v>212396292.8059111</v>
       </c>
       <c r="D104">
-        <v>1267017311</v>
+        <v>208655479.04974186</v>
       </c>
       <c r="E104">
-        <v>2201582135.7442603</v>
+        <v>1322198763</v>
       </c>
       <c r="F104">
-        <v>149414234.21793836</v>
+        <v>2297465986.578746</v>
+      </c>
+      <c r="G104">
+        <v>155921559.97867292</v>
       </c>
     </row>
     <row r="105">
@@ -1881,14 +1898,17 @@
       <c r="B105">
         <v>0</v>
       </c>
-      <c r="D105">
+      <c r="C105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>623449827.881175</v>
+        <v>0</v>
       </c>
       <c r="F105">
-        <v>701607187.3991897</v>
+        <v>650602469.3060818</v>
+      </c>
+      <c r="G105">
+        <v>732163757.5169994</v>
       </c>
     </row>
     <row r="106">
@@ -1896,19 +1916,22 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>15024123840</v>
+        <v>16757811612</v>
       </c>
       <c r="C106">
-        <v>15176838593.28894</v>
+        <v>15678458205.184336</v>
       </c>
       <c r="D106">
-        <v>15282457123</v>
+        <v>15837824029.25862</v>
       </c>
       <c r="E106">
-        <v>15494914820.425539</v>
+        <v>15948042484</v>
       </c>
       <c r="F106">
-        <v>7935240944.699962</v>
+        <v>16169753191.074146</v>
+      </c>
+      <c r="G106">
+        <v>8280838525.060095</v>
       </c>
     </row>
     <row r="107">
@@ -1916,38 +1939,47 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>30950922929</v>
+        <v>33915361856</v>
       </c>
       <c r="C107">
-        <v>31771166617.811516</v>
+        <v>32298905195.53971</v>
       </c>
       <c r="D107">
-        <v>31061313847</v>
+        <v>33154872340.78241</v>
       </c>
       <c r="E107">
-        <v>35022152307.05308</v>
+        <v>32414103886</v>
       </c>
       <c r="F107">
-        <v>20671761747.204544</v>
+        <v>36547445764.513336</v>
+      </c>
+      <c r="G107">
+        <v>21572063438.281322</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="B108">
+        <v>-9823181093</v>
+      </c>
+      <c r="C108">
+        <v>-10076445568.058146</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:I50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -1955,6 +1987,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1962,24 +1995,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1993,25 +2029,28 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>4529796896</v>
+        <v>6263413629</v>
       </c>
       <c r="C3">
-        <v>3592971402.643822</v>
+        <v>4727079733.117385</v>
       </c>
       <c r="D3">
-        <v>4401960694.354961</v>
+        <v>3749453383.6838837</v>
       </c>
       <c r="E3">
-        <v>2794826467</v>
+        <v>4593675977</v>
       </c>
       <c r="F3">
-        <v>1700560153.5488942</v>
+        <v>2916547441.983978</v>
       </c>
       <c r="G3">
-        <v>2256198582.3948956</v>
+        <v>1774623370.8373237</v>
       </c>
       <c r="H3">
-        <v>1108356110.9155314</v>
+        <v>2354461102.250507</v>
+      </c>
+      <c r="I3">
+        <v>1156627510.962384</v>
       </c>
     </row>
     <row r="4">
@@ -2023,36 +2062,51 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
+      <c r="B5">
+        <v>6345411413</v>
+      </c>
+      <c r="C5">
+        <v>4791050511.722349</v>
+      </c>
+      <c r="E5">
+        <v>4744525972</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
+      <c r="E6">
+        <v>637758</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-3942623495</v>
+        <v>-4742970935</v>
       </c>
       <c r="C7">
-        <v>-2948557441.9514394</v>
+        <v>-4114333610.6270604</v>
       </c>
       <c r="D7">
-        <v>-3896631077.15269</v>
+        <v>-3076973746.458474</v>
       </c>
       <c r="E7">
-        <v>-2150070700</v>
+        <v>-4066338119</v>
       </c>
       <c r="F7">
-        <v>-1077668143.3297172</v>
+        <v>-2243711112.0179257</v>
       </c>
       <c r="G7">
-        <v>-1749784616.8689055</v>
+        <v>-1124603013.4063094</v>
       </c>
       <c r="H7">
-        <v>-849703551.199903</v>
+        <v>-1825991670.1840513</v>
+      </c>
+      <c r="I7">
+        <v>-886710050.8594042</v>
       </c>
     </row>
     <row r="8">
@@ -2060,35 +2114,38 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>587173401</v>
+        <v>1520442694</v>
       </c>
       <c r="C8">
-        <v>644413960.6923826</v>
+        <v>612746122.4903244</v>
       </c>
       <c r="D8">
-        <v>505329617.20227194</v>
+        <v>672479637.2254092</v>
       </c>
       <c r="E8">
-        <v>644755767</v>
+        <v>527337858</v>
       </c>
       <c r="F8">
-        <v>622892010.2191771</v>
+        <v>672836329.966052</v>
       </c>
       <c r="G8">
-        <v>506413965.52598995</v>
+        <v>650020357.4310143</v>
       </c>
       <c r="H8">
-        <v>258652559.71562847</v>
+        <v>528469432.0664555</v>
+      </c>
+      <c r="I8">
+        <v>269917460.1029797</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Gelirler</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>0</v>
       </c>
     </row>
@@ -2099,7 +2156,13 @@
       <c r="B10">
         <v>0</v>
       </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>0</v>
       </c>
     </row>
@@ -2110,7 +2173,13 @@
       <c r="B11">
         <v>0</v>
       </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>0</v>
       </c>
     </row>
@@ -2124,25 +2193,28 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>587173401</v>
+        <v>1520442694</v>
       </c>
       <c r="C13">
-        <v>644413960.6923826</v>
+        <v>612746122.4903244</v>
       </c>
       <c r="D13">
-        <v>505329617.20227194</v>
+        <v>672479637.2254092</v>
       </c>
       <c r="E13">
-        <v>644755767</v>
+        <v>527337858</v>
       </c>
       <c r="F13">
-        <v>622892010.2191771</v>
+        <v>672836329.966052</v>
       </c>
       <c r="G13">
-        <v>506413965.52598995</v>
+        <v>650020357.4310143</v>
       </c>
       <c r="H13">
-        <v>258652559.71562847</v>
+        <v>528469432.0664555</v>
+      </c>
+      <c r="I13">
+        <v>269917460.1029797</v>
       </c>
     </row>
     <row r="14"/>
@@ -2151,25 +2223,28 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-252420916</v>
+        <v>-359569403</v>
       </c>
       <c r="C15">
-        <v>-179303312.01550364</v>
+        <v>-263414414.29574543</v>
       </c>
       <c r="D15">
-        <v>-261663043.62484157</v>
+        <v>-187112374.3004371</v>
       </c>
       <c r="E15">
-        <v>-272800477</v>
+        <v>-273059057</v>
       </c>
       <c r="F15">
-        <v>-180303641.36455557</v>
+        <v>-284681550.98745847</v>
       </c>
       <c r="G15">
-        <v>-218393263.0714361</v>
+        <v>-188156270.24122894</v>
       </c>
       <c r="H15">
-        <v>-125152861.38415858</v>
+        <v>-227904780.5931383</v>
+      </c>
+      <c r="I15">
+        <v>-130603549.82209457</v>
       </c>
     </row>
     <row r="16">
@@ -2177,30 +2252,33 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-12847619</v>
+        <v>-18651638</v>
       </c>
       <c r="C16">
-        <v>-9127941.210611174</v>
+        <v>-13407161.686949471</v>
       </c>
       <c r="D16">
-        <v>-10071148.10631607</v>
+        <v>-9525483.568561094</v>
       </c>
       <c r="E16">
-        <v>-6016780</v>
+        <v>-10509769</v>
       </c>
       <c r="F16">
-        <v>-3445801.403027294</v>
+        <v>-6278824.293809136</v>
+      </c>
+      <c r="G16">
+        <v>-3595873.799768212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
         <v xml:space="preserve">    Araştırma ve Geliştirme Giderleri (-)</v>
       </c>
-      <c r="B17">
-        <v>-1469934548</v>
-      </c>
-      <c r="E17">
-        <v>-824007276</v>
+      <c r="C17">
+        <v>-1533953501.7553828</v>
+      </c>
+      <c r="F17">
+        <v>-859894645.1132151</v>
       </c>
     </row>
     <row r="18">
@@ -2208,25 +2286,28 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>1469934548</v>
+        <v>1883886240</v>
       </c>
       <c r="C18">
-        <v>1087171319.9851604</v>
+        <v>1533953501.7553828</v>
       </c>
       <c r="D18">
-        <v>963671256.7700924</v>
+        <v>1134520074.7667973</v>
       </c>
       <c r="E18">
-        <v>824007276</v>
+        <v>1005641307</v>
       </c>
       <c r="F18">
-        <v>273116772.26100755</v>
+        <v>859894645.1132151</v>
       </c>
       <c r="G18">
-        <v>2456891819.8271804</v>
+        <v>285011621.6180667</v>
       </c>
       <c r="H18">
-        <v>753711872.6438539</v>
+        <v>2563894981.300935</v>
+      </c>
+      <c r="I18">
+        <v>786537718.9275007</v>
       </c>
     </row>
     <row r="19">
@@ -2234,25 +2315,28 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-956480995</v>
+        <v>-1642410810</v>
       </c>
       <c r="C19">
-        <v>-699502851.4751371</v>
+        <v>-998137892.3564988</v>
       </c>
       <c r="D19">
-        <v>-728634157.76046</v>
+        <v>-729967773.0332263</v>
       </c>
       <c r="E19">
-        <v>-435239758</v>
+        <v>-760367814</v>
       </c>
       <c r="F19">
-        <v>-73781633.38567191</v>
+        <v>-454195427.81388205</v>
       </c>
       <c r="G19">
-        <v>-977480789.1302962</v>
+        <v>-76994989.36954252</v>
       </c>
       <c r="H19">
-        <v>-380634282.64219373</v>
+        <v>-1020052274.7255225</v>
+      </c>
+      <c r="I19">
+        <v>-397211761.2594144</v>
       </c>
     </row>
     <row r="20">
@@ -2265,25 +2349,28 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>835358419</v>
+        <v>1383697083</v>
       </c>
       <c r="C21">
-        <v>843651175.9762912</v>
+        <v>871740155.9065133</v>
       </c>
       <c r="D21">
-        <v>468632524.48074657</v>
+        <v>880394081.0899823</v>
       </c>
       <c r="E21">
-        <v>754706028</v>
+        <v>489042525</v>
       </c>
       <c r="F21">
-        <v>638477706.3269299</v>
+        <v>787575171.9841174</v>
       </c>
       <c r="G21">
-        <v>1767431733.1514382</v>
+        <v>666284845.6385413</v>
       </c>
       <c r="H21">
-        <v>506577288.33313006</v>
+        <v>1844407358.04873</v>
+      </c>
+      <c r="I21">
+        <v>528639867.94897145</v>
       </c>
     </row>
     <row r="22"/>
@@ -2302,25 +2389,28 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>514397203</v>
+        <v>538970309</v>
       </c>
       <c r="C25">
-        <v>433251462.77647126</v>
+        <v>536800357.47756606</v>
       </c>
       <c r="D25">
-        <v>82214376.00955248</v>
+        <v>452120537.86398244</v>
       </c>
       <c r="E25">
-        <v>35264496</v>
+        <v>85794997</v>
       </c>
       <c r="F25">
-        <v>30388742.039193276</v>
+        <v>36800344.07003997</v>
       </c>
       <c r="G25">
-        <v>170251497.8828799</v>
+        <v>31712240.064284507</v>
       </c>
       <c r="H25">
-        <v>1369920.813831944</v>
+        <v>177666333.31523192</v>
+      </c>
+      <c r="I25">
+        <v>1429583.9446485983</v>
       </c>
     </row>
     <row r="26">
@@ -2328,25 +2418,28 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-464535940</v>
+        <v>-483983206</v>
       </c>
       <c r="C26">
-        <v>-418295448.8599597</v>
+        <v>-484767524.3933571</v>
       </c>
       <c r="D26">
-        <v>-457622878.17065483</v>
+        <v>-436513155.92255527</v>
       </c>
       <c r="E26">
-        <v>-451809629</v>
+        <v>-477553384</v>
       </c>
       <c r="F26">
-        <v>-451991470.75595516</v>
+        <v>-471486953.9424896</v>
       </c>
       <c r="G26">
-        <v>-1803293626.4797122</v>
+        <v>-471676715.31566936</v>
       </c>
       <c r="H26">
-        <v>-876115075.1001893</v>
+        <v>-1881831117.4435487</v>
+      </c>
+      <c r="I26">
+        <v>-914271855.994649</v>
       </c>
     </row>
     <row r="27">
@@ -2359,22 +2452,25 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
       <c r="B28">
-        <v>-273930</v>
+        <v>-76245</v>
       </c>
       <c r="C28">
-        <v>-387966.1137422298</v>
+        <v>-285860.26725310495</v>
       </c>
       <c r="D28">
-        <v>36000837.3667202</v>
+        <v>-404862.91008470167</v>
       </c>
       <c r="E28">
-        <v>38399942</v>
+        <v>37568754</v>
       </c>
       <c r="F28">
-        <v>-6345611.701114563</v>
+        <v>40072345.79134716</v>
       </c>
       <c r="G28">
-        <v>-52156767.89258565</v>
+        <v>-6621977.354671043</v>
+      </c>
+      <c r="H28">
+        <v>-54428312.374813624</v>
       </c>
     </row>
     <row r="29">
@@ -2402,25 +2498,28 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>884945752</v>
+        <v>1438607941</v>
       </c>
       <c r="C33">
-        <v>858219223.7790605</v>
+        <v>923487128.7234691</v>
       </c>
       <c r="D33">
-        <v>129224859.68636441</v>
+        <v>895596600.1213248</v>
       </c>
       <c r="E33">
-        <v>376560837</v>
+        <v>134852892</v>
       </c>
       <c r="F33">
-        <v>210529365.90905347</v>
+        <v>392960907.90301496</v>
       </c>
       <c r="G33">
-        <v>82232836.66202027</v>
+        <v>219698393.03248546</v>
       </c>
       <c r="H33">
-        <v>-368167865.95322734</v>
+        <v>85814261.54559939</v>
+      </c>
+      <c r="I33">
+        <v>-384202404.10102904</v>
       </c>
     </row>
     <row r="34"/>
@@ -2429,25 +2528,28 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>505530568</v>
+        <v>566758643</v>
       </c>
       <c r="C35">
-        <v>345072415.7681863</v>
+        <v>527547560.592465</v>
       </c>
       <c r="D35">
-        <v>1076575090.3761928</v>
+        <v>360101095.1453593</v>
       </c>
       <c r="E35">
-        <v>1099352394</v>
+        <v>1123462356</v>
       </c>
       <c r="F35">
-        <v>273737858.40186834</v>
+        <v>1147231661.9361906</v>
       </c>
       <c r="G35">
-        <v>1795826285.0311892</v>
+        <v>285659757.4564695</v>
       </c>
       <c r="H35">
-        <v>1430758349.8580856</v>
+        <v>1874038556.4894912</v>
+      </c>
+      <c r="I35">
+        <v>1493071092.1222348</v>
       </c>
     </row>
     <row r="36">
@@ -2455,25 +2557,28 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-3787207122</v>
+        <v>-3971908616</v>
       </c>
       <c r="C36">
-        <v>-2958049653.1599245</v>
+        <v>-3952148505.2304688</v>
       </c>
       <c r="D36">
-        <v>-3387600624.827056</v>
+        <v>-3086879364.8021407</v>
       </c>
       <c r="E36">
-        <v>-3206073738</v>
+        <v>-3535138249</v>
       </c>
       <c r="F36">
-        <v>-2026314738.1851623</v>
+        <v>-3345705456.057537</v>
       </c>
       <c r="G36">
-        <v>-4338160454.742163</v>
+        <v>-2114565299.8814144</v>
       </c>
       <c r="H36">
-        <v>-1621033483.841937</v>
+        <v>-4527097094.073106</v>
+      </c>
+      <c r="I36">
+        <v>-1691633135.9007332</v>
       </c>
     </row>
     <row r="37">
@@ -2481,25 +2586,28 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>3207103576</v>
+        <v>3198226260</v>
       </c>
       <c r="C37">
-        <v>2228163960.561119</v>
+        <v>3346780145.8173566</v>
       </c>
       <c r="D37">
-        <v>4878488993.197426</v>
+        <v>2325205509.6182904</v>
       </c>
       <c r="E37">
-        <v>5076606990</v>
+        <v>5090958157</v>
       </c>
       <c r="F37">
-        <v>3651650287.2319765</v>
+        <v>5297704635.8572645</v>
       </c>
       <c r="G37">
-        <v>5829764965.702953</v>
+        <v>3810687865.5970874</v>
       </c>
       <c r="H37">
-        <v>2303229591.8833523</v>
+        <v>6083664334.3870125</v>
+      </c>
+      <c r="I37">
+        <v>2403540417.920764</v>
       </c>
     </row>
     <row r="38">
@@ -2507,25 +2615,28 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>810372774</v>
+        <v>1231684228</v>
       </c>
       <c r="C38">
-        <v>473405946.9484415</v>
+        <v>845666329.9028219</v>
       </c>
       <c r="D38">
-        <v>2696688318.4329267</v>
+        <v>494023840.08283395</v>
       </c>
       <c r="E38">
-        <v>3346446483</v>
+        <v>2814135156</v>
       </c>
       <c r="F38">
-        <v>2109602773.357736</v>
+        <v>3492191749.6389337</v>
       </c>
       <c r="G38">
-        <v>3369663632.6540003</v>
+        <v>2201480716.204628</v>
       </c>
       <c r="H38">
-        <v>1744786591.9462738</v>
+        <v>3516420058.3489976</v>
+      </c>
+      <c r="I38">
+        <v>1820775970.0412366</v>
       </c>
     </row>
     <row r="39"/>
@@ -2534,33 +2645,36 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-606840758</v>
+        <v>-780288440</v>
       </c>
       <c r="C40">
-        <v>-273458623.2950702</v>
+        <v>-633270037.0969108</v>
       </c>
       <c r="D40">
-        <v>-1429671007.5373304</v>
+        <v>-285368361.033092</v>
       </c>
       <c r="E40">
-        <v>-2057820158</v>
+        <v>-1491936393</v>
       </c>
       <c r="F40">
-        <v>-1300967964.4455378</v>
+        <v>-2147442851.548595</v>
       </c>
       <c r="G40">
-        <v>-1170772332.6648936</v>
+        <v>-1357628043.6758637</v>
       </c>
       <c r="H40">
-        <v>-1528801234.5975857</v>
+        <v>-1221762099.4711335</v>
+      </c>
+      <c r="I40">
+        <v>-1595383964.877679</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="G41">
-        <v>-5038341.215949326</v>
+      <c r="H41">
+        <v>-5257772.301331026</v>
       </c>
     </row>
     <row r="42">
@@ -2568,25 +2682,28 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-606840758</v>
+        <v>-780288440</v>
       </c>
       <c r="C42">
-        <v>-273458623.2950702</v>
+        <v>-633270037.0969108</v>
       </c>
       <c r="D42">
-        <v>-1429671007.5373304</v>
+        <v>-285368361.033092</v>
       </c>
       <c r="E42">
-        <v>-2057820158</v>
+        <v>-1491936393</v>
       </c>
       <c r="F42">
-        <v>-1300967964.4455378</v>
+        <v>-2147442851.548595</v>
       </c>
       <c r="G42">
-        <v>-1165733991.4489443</v>
+        <v>-1357628043.6758637</v>
       </c>
       <c r="H42">
-        <v>-1528801234.5975857</v>
+        <v>-1216504327.1698024</v>
+      </c>
+      <c r="I42">
+        <v>-1595383964.877679</v>
       </c>
     </row>
     <row r="43">
@@ -2594,35 +2711,38 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>203532016</v>
+        <v>451395788</v>
       </c>
       <c r="C43">
-        <v>199947323.6533713</v>
+        <v>212396292.8059111</v>
       </c>
       <c r="D43">
-        <v>1267017310.8955963</v>
+        <v>208655479.04974186</v>
       </c>
       <c r="E43">
-        <v>1288626325</v>
+        <v>1322198763</v>
       </c>
       <c r="F43">
-        <v>808634808.9121983</v>
+        <v>1344748898.0903387</v>
       </c>
       <c r="G43">
-        <v>2198891299.9891067</v>
+        <v>843852672.5287645</v>
       </c>
       <c r="H43">
-        <v>215985357.34868798</v>
+        <v>2294657958.8778644</v>
+      </c>
+      <c r="I43">
+        <v>225392005.16355753</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetler Dönem Karı/Zararı</v>
       </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="E44">
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="F44">
         <v>0</v>
       </c>
     </row>
@@ -2632,25 +2752,28 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>203532016</v>
+        <v>451395788</v>
       </c>
       <c r="C46">
-        <v>199947323.6533713</v>
+        <v>212396292.8059111</v>
       </c>
       <c r="D46">
-        <v>1267017310.8955963</v>
+        <v>208655479.04974186</v>
       </c>
       <c r="E46">
-        <v>1288626325</v>
+        <v>1322198763</v>
       </c>
       <c r="F46">
-        <v>808634808.9121983</v>
+        <v>1344748898.0903387</v>
       </c>
       <c r="G46">
-        <v>2198891301.0641503</v>
+        <v>843852672.5287645</v>
       </c>
       <c r="H46">
-        <v>215985357.34868798</v>
+        <v>2294657959.9997287</v>
+      </c>
+      <c r="I46">
+        <v>225392005.16355753</v>
       </c>
     </row>
     <row r="47">
@@ -2660,7 +2783,13 @@
       <c r="B47">
         <v>0</v>
       </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
       <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
         <v>0</v>
       </c>
     </row>
@@ -2669,25 +2798,28 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>203532016</v>
+        <v>451395788</v>
       </c>
       <c r="C48">
-        <v>199947323.6533713</v>
+        <v>212396292.8059111</v>
       </c>
       <c r="D48">
-        <v>1267017310.8955963</v>
+        <v>208655479.04974186</v>
       </c>
       <c r="E48">
-        <v>1288626325</v>
+        <v>1322198763</v>
       </c>
       <c r="F48">
-        <v>808634808.9121983</v>
+        <v>1344748898.0903387</v>
       </c>
       <c r="G48">
-        <v>2198891301.0641503</v>
+        <v>843852672.5287645</v>
       </c>
       <c r="H48">
-        <v>215985357.34868798</v>
+        <v>2294657959.9997287</v>
+      </c>
+      <c r="I48">
+        <v>225392005.16355753</v>
       </c>
     </row>
     <row r="49"/>
@@ -2696,39 +2828,42 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>503667788</v>
+        <v>714563218</v>
       </c>
       <c r="C50">
-        <v>337739246.23859495</v>
+        <v>525603652.336218</v>
       </c>
       <c r="D50">
-        <v>887469719.0976033</v>
+        <v>352448549.59890103</v>
       </c>
       <c r="E50">
-        <v>574185957</v>
+        <v>916682238</v>
       </c>
       <c r="F50">
-        <v>567709101.4791918</v>
+        <v>599193046.1103195</v>
       </c>
       <c r="G50">
-        <v>565706695.8348813</v>
+        <v>592434108.9725909</v>
       </c>
       <c r="H50">
-        <v>406482909.2984353</v>
+        <v>590344494.0613664</v>
+      </c>
+      <c r="I50">
+        <v>424186153.71032864</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:I50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -2736,6 +2871,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2743,24 +2879,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2774,13 +2913,16 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>936825493.3561778</v>
-      </c>
-      <c r="D3">
-        <v>1607134227.3549614</v>
+        <v>1536333895.882615</v>
+      </c>
+      <c r="C3">
+        <v>977626349.4335012</v>
       </c>
       <c r="E3">
-        <v>1094266313.4511058</v>
+        <v>1677128535.0160222</v>
+      </c>
+      <c r="F3">
+        <v>1141924071.1466541</v>
       </c>
     </row>
     <row r="4">
@@ -2792,6 +2934,9 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
+      <c r="B5">
+        <v>1554360901.2776508</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -2803,13 +2948,16 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-994066053.0485606</v>
-      </c>
-      <c r="D7">
-        <v>-1746560377.15269</v>
+        <v>-628637324.3729396</v>
+      </c>
+      <c r="C7">
+        <v>-1037359864.1685863</v>
       </c>
       <c r="E7">
-        <v>-1072402556.6702828</v>
+        <v>-1822627006.9820743</v>
+      </c>
+      <c r="F7">
+        <v>-1119108098.6116164</v>
       </c>
     </row>
     <row r="8">
@@ -2817,13 +2965,16 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>-57240559.692382574</v>
-      </c>
-      <c r="D8">
-        <v>-139426149.79772806</v>
+        <v>907696571.5096756</v>
+      </c>
+      <c r="C8">
+        <v>-59733514.73508477</v>
       </c>
       <c r="E8">
-        <v>21863756.780822873</v>
+        <v>-145498471.96605206</v>
+      </c>
+      <c r="F8">
+        <v>22815972.535037756</v>
       </c>
     </row>
     <row r="9">
@@ -2835,11 +2986,23 @@
       <c r="A10" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -2851,13 +3014,16 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>-57240559.692382574</v>
-      </c>
-      <c r="D13">
-        <v>-139426149.79772806</v>
+        <v>907696571.5096756</v>
+      </c>
+      <c r="C13">
+        <v>-59733514.73508477</v>
       </c>
       <c r="E13">
-        <v>21863756.780822873</v>
+        <v>-145498471.96605206</v>
+      </c>
+      <c r="F13">
+        <v>22815972.535037756</v>
       </c>
     </row>
     <row r="14"/>
@@ -2866,13 +3032,16 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-73117603.98449636</v>
-      </c>
-      <c r="D15">
-        <v>11137433.37515843</v>
+        <v>-96154988.70425457</v>
+      </c>
+      <c r="C15">
+        <v>-76302039.99530834</v>
       </c>
       <c r="E15">
-        <v>-92496835.63544443</v>
+        <v>11622493.987458467</v>
+      </c>
+      <c r="F15">
+        <v>-96525280.74622953</v>
       </c>
     </row>
     <row r="16">
@@ -2880,13 +3049,16 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-3719677.789388826</v>
-      </c>
-      <c r="D16">
-        <v>-4054368.106316069</v>
+        <v>-5244476.313050529</v>
+      </c>
+      <c r="C16">
+        <v>-3881678.118388377</v>
       </c>
       <c r="E16">
-        <v>-2570978.596972706</v>
+        <v>-4230944.706190864</v>
+      </c>
+      <c r="F16">
+        <v>-2682950.4940409246</v>
       </c>
     </row>
     <row r="17">
@@ -2899,13 +3071,16 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>382763228.01483965</v>
-      </c>
-      <c r="D18">
-        <v>139663980.77009237</v>
+        <v>349932738.2446172</v>
+      </c>
+      <c r="C18">
+        <v>399433426.9885855</v>
       </c>
       <c r="E18">
-        <v>550890503.7389925</v>
+        <v>145746661.8867849</v>
+      </c>
+      <c r="F18">
+        <v>574883023.4951484</v>
       </c>
     </row>
     <row r="19">
@@ -2913,13 +3088,16 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-256978143.5248629</v>
-      </c>
-      <c r="D19">
-        <v>-293394399.76046</v>
+        <v>-644272917.6435012</v>
+      </c>
+      <c r="C19">
+        <v>-268170119.3232726</v>
       </c>
       <c r="E19">
-        <v>-361458124.6143281</v>
+        <v>-306172386.18611795</v>
+      </c>
+      <c r="F19">
+        <v>-377200438.4443395</v>
       </c>
     </row>
     <row r="20">
@@ -2932,13 +3110,16 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>-8292756.97629118</v>
-      </c>
-      <c r="D21">
-        <v>-286073503.51925343</v>
+        <v>511956927.09348667</v>
+      </c>
+      <c r="C21">
+        <v>-8653925.183468938</v>
       </c>
       <c r="E21">
-        <v>116228321.67307007</v>
+        <v>-298532646.9841174</v>
+      </c>
+      <c r="F21">
+        <v>121290326.34557605</v>
       </c>
     </row>
     <row r="22"/>
@@ -2957,13 +3138,16 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>81145740.22352874</v>
-      </c>
-      <c r="D25">
-        <v>46949880.00955248</v>
+        <v>2169951.5224339366</v>
+      </c>
+      <c r="C25">
+        <v>84679819.61358362</v>
       </c>
       <c r="E25">
-        <v>4875753.960806724</v>
+        <v>48994652.92996003</v>
+      </c>
+      <c r="F25">
+        <v>5088104.0057554655</v>
       </c>
     </row>
     <row r="26">
@@ -2971,13 +3155,16 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-46240491.14004028</v>
-      </c>
-      <c r="D26">
-        <v>-5813249.170654833</v>
+        <v>784318.3933570981</v>
+      </c>
+      <c r="C26">
+        <v>-48254368.47080183</v>
       </c>
       <c r="E26">
-        <v>181841.75595515966</v>
+        <v>-6066430.057510376</v>
+      </c>
+      <c r="F26">
+        <v>189761.37317973375</v>
       </c>
     </row>
     <row r="27">
@@ -2990,13 +3177,16 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
       <c r="B28">
-        <v>114036.11374222982</v>
-      </c>
-      <c r="D28">
-        <v>-2399104.6332798004</v>
+        <v>209615.26725310495</v>
+      </c>
+      <c r="C28">
+        <v>119002.64283159672</v>
       </c>
       <c r="E28">
-        <v>44745553.701114565</v>
+        <v>-2503591.791347161</v>
+      </c>
+      <c r="F28">
+        <v>46694323.14601821</v>
       </c>
     </row>
     <row r="29">
@@ -3024,13 +3214,16 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>26726528.220939517</v>
-      </c>
-      <c r="D33">
-        <v>-247335977.3136356</v>
+        <v>515120812.27653086</v>
+      </c>
+      <c r="C33">
+        <v>27890528.60214436</v>
       </c>
       <c r="E33">
-        <v>166031471.09094653</v>
+        <v>-258108015.90301496</v>
+      </c>
+      <c r="F33">
+        <v>173262514.8705295</v>
       </c>
     </row>
     <row r="34"/>
@@ -3039,13 +3232,16 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>160458152.23181373</v>
-      </c>
-      <c r="D35">
-        <v>-22777303.62380719</v>
+        <v>39211082.40753502</v>
+      </c>
+      <c r="C35">
+        <v>167446465.4471057</v>
       </c>
       <c r="E35">
-        <v>825614535.5981317</v>
+        <v>-23769305.936190605</v>
+      </c>
+      <c r="F35">
+        <v>861571904.4797211</v>
       </c>
     </row>
     <row r="36">
@@ -3053,13 +3249,16 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-829157468.8400755</v>
-      </c>
-      <c r="D36">
-        <v>-181526886.82705593</v>
+        <v>-19760110.76953125</v>
+      </c>
+      <c r="C36">
+        <v>-865269140.428328</v>
       </c>
       <c r="E36">
-        <v>-1179758999.8148377</v>
+        <v>-189432792.94246292</v>
+      </c>
+      <c r="F36">
+        <v>-1231140156.1761227</v>
       </c>
     </row>
     <row r="37">
@@ -3067,13 +3266,16 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>978939615.4388809</v>
-      </c>
-      <c r="D37">
-        <v>-198117996.80257416</v>
+        <v>-148553885.8173566</v>
+      </c>
+      <c r="C37">
+        <v>1021574636.1990662</v>
       </c>
       <c r="E37">
-        <v>1424956702.7680235</v>
+        <v>-206746478.85726452</v>
+      </c>
+      <c r="F37">
+        <v>1487016770.2601771</v>
       </c>
     </row>
     <row r="38">
@@ -3081,13 +3283,16 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>336966827.0515585</v>
-      </c>
-      <c r="D38">
-        <v>-649758164.5670733</v>
+        <v>386017898.0971781</v>
+      </c>
+      <c r="C38">
+        <v>351642489.81998795</v>
       </c>
       <c r="E38">
-        <v>1236843709.642264</v>
+        <v>-678056593.6389337</v>
+      </c>
+      <c r="F38">
+        <v>1290711033.4343057</v>
       </c>
     </row>
     <row r="39"/>
@@ -3096,13 +3301,16 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-333382134.7049298</v>
-      </c>
-      <c r="D40">
-        <v>628149150.4626696</v>
+        <v>-147018402.90308917</v>
+      </c>
+      <c r="C40">
+        <v>-347901676.0638188</v>
       </c>
       <c r="E40">
-        <v>-756852193.5544622</v>
+        <v>655506458.548595</v>
+      </c>
+      <c r="F40">
+        <v>-789814807.8727312</v>
       </c>
     </row>
     <row r="41">
@@ -3115,13 +3323,16 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-333382134.7049298</v>
-      </c>
-      <c r="D42">
-        <v>628149150.4626696</v>
+        <v>-147018402.90308917</v>
+      </c>
+      <c r="C42">
+        <v>-347901676.0638188</v>
       </c>
       <c r="E42">
-        <v>-756852193.5544622</v>
+        <v>655506458.548595</v>
+      </c>
+      <c r="F42">
+        <v>-789814807.8727312</v>
       </c>
     </row>
     <row r="43">
@@ -3129,13 +3340,16 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>3584692.3466286957</v>
-      </c>
-      <c r="D43">
-        <v>-21609014.104403734</v>
+        <v>238999495.1940889</v>
+      </c>
+      <c r="C43">
+        <v>3740813.7561692297</v>
       </c>
       <c r="E43">
-        <v>479991516.0878017</v>
+        <v>-22550135.090338707</v>
+      </c>
+      <c r="F43">
+        <v>500896225.5615742</v>
       </c>
     </row>
     <row r="44">
@@ -3149,32 +3363,44 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>3584692.3466286957</v>
-      </c>
-      <c r="D46">
-        <v>-21609014.104403734</v>
+        <v>238999495.1940889</v>
+      </c>
+      <c r="C46">
+        <v>3740813.7561692297</v>
       </c>
       <c r="E46">
-        <v>479991516.0878017</v>
+        <v>-22550135.090338707</v>
+      </c>
+      <c r="F46">
+        <v>500896225.5615742</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>3584692.3466286957</v>
-      </c>
-      <c r="D48">
-        <v>-21609014.104403734</v>
+        <v>238999495.1940889</v>
+      </c>
+      <c r="C48">
+        <v>3740813.7561692297</v>
       </c>
       <c r="E48">
-        <v>479991516.0878017</v>
+        <v>-22550135.090338707</v>
+      </c>
+      <c r="F48">
+        <v>500896225.5615742</v>
       </c>
     </row>
     <row r="49"/>
@@ -3183,27 +3409,30 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>165928541.76140505</v>
-      </c>
-      <c r="D50">
-        <v>313283762.0976033</v>
+        <v>188959565.663782</v>
+      </c>
+      <c r="C50">
+        <v>173155102.73731697</v>
       </c>
       <c r="E50">
-        <v>6476855.52080822</v>
+        <v>317489191.8896805</v>
+      </c>
+      <c r="F50">
+        <v>6758937.137728572</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:I50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -3211,6 +3440,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3218,24 +3448,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3249,19 +3482,22 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>6136931123.354961</v>
+        <v>6263413629</v>
       </c>
       <c r="C3">
-        <v>6294371943.44989</v>
+        <v>6404208268.133408</v>
       </c>
       <c r="D3">
-        <v>4401960694.354961</v>
-      </c>
-      <c r="G3">
-        <v>2256198582.3948956</v>
+        <v>6568505989.84656</v>
+      </c>
+      <c r="E3">
+        <v>4593675977</v>
       </c>
       <c r="H3">
-        <v>1108356110.9155314</v>
+        <v>2354461102.250507</v>
+      </c>
+      <c r="I3">
+        <v>1156627510.962384</v>
       </c>
     </row>
     <row r="4">
@@ -3273,30 +3509,42 @@
       <c r="A5" t="str">
         <v xml:space="preserve">    Yurt İçi Satışlar</v>
       </c>
+      <c r="B5">
+        <v>6345411413</v>
+      </c>
+      <c r="E5">
+        <v>4744525972</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Yurt Dışı Satışlar</v>
       </c>
+      <c r="E6">
+        <v>637758</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-5689183872.15269</v>
+        <v>-4742970935</v>
       </c>
       <c r="C7">
-        <v>-5767520375.774412</v>
+        <v>-5936960617.609135</v>
       </c>
       <c r="D7">
-        <v>-3896631077.15269</v>
-      </c>
-      <c r="G7">
-        <v>-1749784616.8689055</v>
+        <v>-6018708852.052165</v>
+      </c>
+      <c r="E7">
+        <v>-4066338119</v>
       </c>
       <c r="H7">
-        <v>-849703551.199903</v>
+        <v>-1825991670.1840513</v>
+      </c>
+      <c r="I7">
+        <v>-886710050.8594042</v>
       </c>
     </row>
     <row r="8">
@@ -3304,19 +3552,22 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>447747251.20227194</v>
+        <v>1520442694</v>
       </c>
       <c r="C8">
-        <v>526851567.6754774</v>
+        <v>467247650.5242723</v>
       </c>
       <c r="D8">
-        <v>505329617.20227194</v>
-      </c>
-      <c r="G8">
-        <v>506413965.52598995</v>
+        <v>549797137.7943949</v>
+      </c>
+      <c r="E8">
+        <v>527337858</v>
       </c>
       <c r="H8">
-        <v>258652559.71562847</v>
+        <v>528469432.0664555</v>
+      </c>
+      <c r="I8">
+        <v>269917460.1029797</v>
       </c>
     </row>
     <row r="9">
@@ -3328,11 +3579,29 @@
       <c r="A10" t="str">
         <v xml:space="preserve">    Faiz, Ücret, Prim, Komisyon ve Diğer Giderler (-)</v>
       </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Brüt Kar (Zarar)</v>
       </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -3344,19 +3613,22 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>447747251.20227194</v>
+        <v>1520442694</v>
       </c>
       <c r="C13">
-        <v>526851567.6754774</v>
+        <v>467247650.5242723</v>
       </c>
       <c r="D13">
-        <v>505329617.20227194</v>
-      </c>
-      <c r="G13">
-        <v>506413965.52598995</v>
+        <v>549797137.7943949</v>
+      </c>
+      <c r="E13">
+        <v>527337858</v>
       </c>
       <c r="H13">
-        <v>258652559.71562847</v>
+        <v>528469432.0664555</v>
+      </c>
+      <c r="I13">
+        <v>269917460.1029797</v>
       </c>
     </row>
     <row r="14"/>
@@ -3365,19 +3637,22 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-241283482.62484157</v>
+        <v>-359569403</v>
       </c>
       <c r="C15">
-        <v>-260662714.27578965</v>
+        <v>-251791920.30828696</v>
       </c>
       <c r="D15">
-        <v>-261663043.62484157</v>
-      </c>
-      <c r="G15">
-        <v>-218393263.0714361</v>
+        <v>-272015161.05920815</v>
+      </c>
+      <c r="E15">
+        <v>-273059057</v>
       </c>
       <c r="H15">
-        <v>-125152861.38415858</v>
+        <v>-227904780.5931383</v>
+      </c>
+      <c r="I15">
+        <v>-130603549.82209457</v>
       </c>
     </row>
     <row r="16">
@@ -3385,13 +3660,16 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-16901987.106316067</v>
+        <v>-18651638</v>
       </c>
       <c r="C16">
-        <v>-15753287.913899949</v>
+        <v>-17638106.393140335</v>
       </c>
       <c r="D16">
-        <v>-10071148.10631607</v>
+        <v>-16439378.768792883</v>
+      </c>
+      <c r="E16">
+        <v>-10509769</v>
       </c>
     </row>
     <row r="17">
@@ -3404,19 +3682,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>1609598528.7700925</v>
+        <v>1883886240</v>
       </c>
       <c r="C18">
-        <v>1777725804.494245</v>
+        <v>1679700163.6421676</v>
       </c>
       <c r="D18">
-        <v>963671256.7700924</v>
-      </c>
-      <c r="G18">
-        <v>2456891819.8271804</v>
+        <v>1855149760.1487305</v>
+      </c>
+      <c r="E18">
+        <v>1005641307</v>
       </c>
       <c r="H18">
-        <v>753711872.6438539</v>
+        <v>2563894981.300935</v>
+      </c>
+      <c r="I18">
+        <v>786537718.9275007</v>
       </c>
     </row>
     <row r="19">
@@ -3424,19 +3705,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-1249875394.76046</v>
+        <v>-1642410810</v>
       </c>
       <c r="C19">
-        <v>-1354355375.849925</v>
+        <v>-1304310278.5426168</v>
       </c>
       <c r="D19">
-        <v>-728634157.76046</v>
-      </c>
-      <c r="G19">
-        <v>-977480789.1302962</v>
+        <v>-1413340597.663684</v>
+      </c>
+      <c r="E19">
+        <v>-760367814</v>
       </c>
       <c r="H19">
-        <v>-380634282.64219373</v>
+        <v>-1020052274.7255225</v>
+      </c>
+      <c r="I19">
+        <v>-397211761.2594144</v>
       </c>
     </row>
     <row r="20">
@@ -3449,19 +3733,22 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>549284915.4807465</v>
+        <v>1383697083</v>
       </c>
       <c r="C21">
-        <v>673805994.1301079</v>
+        <v>573207508.922396</v>
       </c>
       <c r="D21">
-        <v>468632524.48074657</v>
-      </c>
-      <c r="G21">
-        <v>1767431733.1514382</v>
+        <v>703151760.4514409</v>
+      </c>
+      <c r="E21">
+        <v>489042525</v>
       </c>
       <c r="H21">
-        <v>506577288.33313006</v>
+        <v>1844407358.04873</v>
+      </c>
+      <c r="I21">
+        <v>528639867.94897145</v>
       </c>
     </row>
     <row r="22"/>
@@ -3480,19 +3767,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>561347083.0095525</v>
+        <v>538970309</v>
       </c>
       <c r="C25">
-        <v>485077096.74683046</v>
+        <v>585795010.4075261</v>
       </c>
       <c r="D25">
-        <v>82214376.00955248</v>
-      </c>
-      <c r="G25">
-        <v>170251497.8828799</v>
+        <v>506203294.79969794</v>
+      </c>
+      <c r="E25">
+        <v>85794997</v>
       </c>
       <c r="H25">
-        <v>1369920.813831944</v>
+        <v>177666333.31523192</v>
+      </c>
+      <c r="I25">
+        <v>1429583.9446485983</v>
       </c>
     </row>
     <row r="26">
@@ -3500,19 +3790,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-470349189.17065483</v>
+        <v>-483983206</v>
       </c>
       <c r="C26">
-        <v>-423926856.2746594</v>
+        <v>-490833954.4508675</v>
       </c>
       <c r="D26">
-        <v>-457622878.17065483</v>
-      </c>
-      <c r="G26">
-        <v>-1803293626.4797122</v>
+        <v>-442389824.6068859</v>
+      </c>
+      <c r="E26">
+        <v>-477553384</v>
       </c>
       <c r="H26">
-        <v>-876115075.1001893</v>
+        <v>-1881831117.4435487</v>
+      </c>
+      <c r="I26">
+        <v>-914271855.994649</v>
       </c>
     </row>
     <row r="27">
@@ -3525,16 +3818,19 @@
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
       <c r="B28">
-        <v>-2673034.6332798004</v>
+        <v>-76245</v>
       </c>
       <c r="C28">
-        <v>41958482.95409253</v>
+        <v>-2789452.058600266</v>
       </c>
       <c r="D28">
-        <v>36000837.3667202</v>
-      </c>
-      <c r="G28">
-        <v>-52156767.89258565</v>
+        <v>43785868.444586344</v>
+      </c>
+      <c r="E28">
+        <v>37568754</v>
+      </c>
+      <c r="H28">
+        <v>-54428312.374813624</v>
       </c>
     </row>
     <row r="29">
@@ -3562,19 +3858,22 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>637609774.6863644</v>
+        <v>1438607941</v>
       </c>
       <c r="C33">
-        <v>776914717.5563715</v>
+        <v>665379112.8204541</v>
       </c>
       <c r="D33">
-        <v>129224859.68636441</v>
-      </c>
-      <c r="G33">
-        <v>82232836.66202027</v>
+        <v>810751099.0888393</v>
+      </c>
+      <c r="E33">
+        <v>134852892</v>
       </c>
       <c r="H33">
-        <v>-368167865.95322734</v>
+        <v>85814261.54559939</v>
+      </c>
+      <c r="I33">
+        <v>-384202404.10102904</v>
       </c>
     </row>
     <row r="34"/>
@@ -3583,19 +3882,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>482753264.3761928</v>
+        <v>566758643</v>
       </c>
       <c r="C35">
-        <v>1147909647.7425108</v>
+        <v>503778254.6562744</v>
       </c>
       <c r="D35">
-        <v>1076575090.3761928</v>
-      </c>
-      <c r="G35">
-        <v>1795826285.0311892</v>
+        <v>1197903693.6888897</v>
+      </c>
+      <c r="E35">
+        <v>1123462356</v>
       </c>
       <c r="H35">
-        <v>1430758349.8580856</v>
+        <v>1874038556.4894912</v>
+      </c>
+      <c r="I35">
+        <v>1493071092.1222348</v>
       </c>
     </row>
     <row r="36">
@@ -3603,19 +3905,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-3968734008.827056</v>
+        <v>-3971908616</v>
       </c>
       <c r="C36">
-        <v>-4319335539.801818</v>
+        <v>-4141581298.1729317</v>
       </c>
       <c r="D36">
-        <v>-3387600624.827056</v>
-      </c>
-      <c r="G36">
-        <v>-4338160454.742163</v>
+        <v>-4507452313.920727</v>
+      </c>
+      <c r="E36">
+        <v>-3535138249</v>
       </c>
       <c r="H36">
-        <v>-1621033483.841937</v>
+        <v>-4527097094.073106</v>
+      </c>
+      <c r="I36">
+        <v>-1691633135.9007332</v>
       </c>
     </row>
     <row r="37">
@@ -3623,19 +3928,22 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>3008985579.197426</v>
+        <v>3198226260</v>
       </c>
       <c r="C37">
-        <v>3455002666.5265684</v>
+        <v>3140033666.960092</v>
       </c>
       <c r="D37">
-        <v>4878488993.197426</v>
-      </c>
-      <c r="G37">
-        <v>5829764965.702953</v>
+        <v>3605475801.021203</v>
+      </c>
+      <c r="E37">
+        <v>5090958157</v>
       </c>
       <c r="H37">
-        <v>2303229591.8833523</v>
+        <v>6083664334.3870125</v>
+      </c>
+      <c r="I37">
+        <v>2403540417.920764</v>
       </c>
     </row>
     <row r="38">
@@ -3643,19 +3951,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>160614609.43292665</v>
+        <v>1231684228</v>
       </c>
       <c r="C38">
-        <v>1060491492.023632</v>
+        <v>167609736.26388824</v>
       </c>
       <c r="D38">
-        <v>2696688318.4329267</v>
-      </c>
-      <c r="G38">
-        <v>3369663632.6540003</v>
+        <v>1106678279.878206</v>
+      </c>
+      <c r="E38">
+        <v>2814135156</v>
       </c>
       <c r="H38">
-        <v>1744786591.9462738</v>
+        <v>3516420058.3489976</v>
+      </c>
+      <c r="I38">
+        <v>1820775970.0412366</v>
       </c>
     </row>
     <row r="39"/>
@@ -3664,27 +3975,30 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>21308392.46266961</v>
+        <v>-780288440</v>
       </c>
       <c r="C40">
-        <v>-402161666.38686275</v>
+        <v>22236421.451684117</v>
       </c>
       <c r="D40">
-        <v>-1429671007.5373304</v>
-      </c>
-      <c r="G40">
-        <v>-1170772332.6648936</v>
+        <v>-419676710.3572283</v>
+      </c>
+      <c r="E40">
+        <v>-1491936393</v>
       </c>
       <c r="H40">
-        <v>-1528801234.5975857</v>
+        <v>-1221762099.4711335</v>
+      </c>
+      <c r="I40">
+        <v>-1595383964.877679</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
-      <c r="G41">
-        <v>-5038341.215949326</v>
+      <c r="H41">
+        <v>-5257772.301331026</v>
       </c>
     </row>
     <row r="42">
@@ -3692,19 +4006,22 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>21308392.46266961</v>
+        <v>-780288440</v>
       </c>
       <c r="C42">
-        <v>-402161666.38686275</v>
+        <v>22236421.451684117</v>
       </c>
       <c r="D42">
-        <v>-1429671007.5373304</v>
-      </c>
-      <c r="G42">
-        <v>-1165733991.4489443</v>
+        <v>-419676710.3572283</v>
+      </c>
+      <c r="E42">
+        <v>-1491936393</v>
       </c>
       <c r="H42">
-        <v>-1528801234.5975857</v>
+        <v>-1216504327.1698024</v>
+      </c>
+      <c r="I42">
+        <v>-1595383964.877679</v>
       </c>
     </row>
     <row r="43">
@@ -3712,19 +4029,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>181923001.89559627</v>
+        <v>451395788</v>
       </c>
       <c r="C43">
-        <v>658329825.6367693</v>
+        <v>189846157.7155724</v>
       </c>
       <c r="D43">
-        <v>1267017310.8955963</v>
-      </c>
-      <c r="G43">
-        <v>2198891299.9891067</v>
+        <v>687001569.5209774</v>
+      </c>
+      <c r="E43">
+        <v>1322198763</v>
       </c>
       <c r="H43">
-        <v>215985357.34868798</v>
+        <v>2294657958.8778644</v>
+      </c>
+      <c r="I43">
+        <v>225392005.16355753</v>
       </c>
     </row>
     <row r="44">
@@ -3738,44 +4058,59 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>181923001.89559627</v>
+        <v>451395788</v>
       </c>
       <c r="C46">
-        <v>658329825.6367693</v>
+        <v>189846157.7155724</v>
       </c>
       <c r="D46">
-        <v>1267017310.8955963</v>
-      </c>
-      <c r="G46">
-        <v>2198891301.0641503</v>
+        <v>687001569.5209774</v>
+      </c>
+      <c r="E46">
+        <v>1322198763</v>
       </c>
       <c r="H46">
-        <v>215985357.34868798</v>
+        <v>2294657959.9997287</v>
+      </c>
+      <c r="I46">
+        <v>225392005.16355753</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>181923001.89559627</v>
+        <v>451395788</v>
       </c>
       <c r="C48">
-        <v>658329825.6367693</v>
+        <v>189846157.7155724</v>
       </c>
       <c r="D48">
-        <v>1267017310.8955963</v>
-      </c>
-      <c r="G48">
-        <v>2198891301.0641503</v>
+        <v>687001569.5209774</v>
+      </c>
+      <c r="E48">
+        <v>1322198763</v>
       </c>
       <c r="H48">
-        <v>215985357.34868798</v>
+        <v>2294657959.9997287</v>
+      </c>
+      <c r="I48">
+        <v>225392005.16355753</v>
       </c>
     </row>
     <row r="49"/>
@@ -3784,33 +4119,36 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>816951550.0976033</v>
+        <v>714563218</v>
       </c>
       <c r="C50">
-        <v>657499863.8570065</v>
+        <v>843092844.2258985</v>
       </c>
       <c r="D50">
-        <v>887469719.0976033</v>
-      </c>
-      <c r="G50">
-        <v>565706695.8348813</v>
+        <v>676696678.6263101</v>
+      </c>
+      <c r="E50">
+        <v>916682238</v>
       </c>
       <c r="H50">
-        <v>406482909.2984353</v>
+        <v>590344494.0613664</v>
+      </c>
+      <c r="I50">
+        <v>424186153.71032864</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:I129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -3818,6 +4156,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3825,24 +4164,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3856,25 +4198,28 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>3530246236</v>
+        <v>3998368466</v>
       </c>
       <c r="C3">
-        <v>-241023538.57066506</v>
+        <v>3683996395.0360594</v>
       </c>
       <c r="D3">
-        <v>3246260496.4647384</v>
+        <v>-251520655.45978665</v>
       </c>
       <c r="E3">
-        <v>5367805765</v>
+        <v>3544445704</v>
       </c>
       <c r="F3">
-        <v>2787888858.87418</v>
+        <v>5601585772.079207</v>
       </c>
       <c r="G3">
-        <v>5705321272.024916</v>
+        <v>2909307685.429587</v>
       </c>
       <c r="H3">
-        <v>-1385426114.937746</v>
+        <v>5953800838.118742</v>
+      </c>
+      <c r="I3">
+        <v>-1445764536.471124</v>
       </c>
     </row>
     <row r="4">
@@ -3882,25 +4227,28 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>203532016</v>
+        <v>451395789</v>
       </c>
       <c r="C4">
-        <v>199947323.6533713</v>
+        <v>212396292.8059111</v>
       </c>
       <c r="D4">
-        <v>1267017310.8955963</v>
+        <v>208655479.04974186</v>
       </c>
       <c r="E4">
-        <v>1288626325</v>
+        <v>1322198763</v>
       </c>
       <c r="F4">
-        <v>808634808.9121983</v>
+        <v>1344748898.0903387</v>
       </c>
       <c r="G4">
-        <v>2201582135.7442603</v>
+        <v>843852672.5287645</v>
       </c>
       <c r="H4">
-        <v>149414234.21793836</v>
+        <v>2297465986.578746</v>
+      </c>
+      <c r="I4">
+        <v>155921559.97867292</v>
       </c>
     </row>
     <row r="5">
@@ -3908,25 +4256,28 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>5190980134</v>
+        <v>244606834</v>
       </c>
       <c r="C5">
-        <v>1676534546.4250727</v>
+        <v>5417058987.371951</v>
       </c>
       <c r="D5">
-        <v>946574341.4640968</v>
+        <v>1749551394.5173378</v>
       </c>
       <c r="E5">
-        <v>6306300510</v>
+        <v>2583671536</v>
       </c>
       <c r="F5">
-        <v>-515912446.3900299</v>
+        <v>6580954072.817843</v>
       </c>
       <c r="G5">
-        <v>1513046764.1354845</v>
+        <v>-538381593.1232692</v>
       </c>
       <c r="H5">
-        <v>1388773171.4158683</v>
+        <v>1578943351.8132925</v>
+      </c>
+      <c r="I5">
+        <v>1449257364.7825437</v>
       </c>
     </row>
     <row r="6">
@@ -3934,25 +4285,28 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>503667788</v>
+        <v>714563218</v>
       </c>
       <c r="C6">
-        <v>337739246.23859495</v>
+        <v>525603652.336218</v>
       </c>
       <c r="D6">
-        <v>887469719.0976033</v>
+        <v>352448549.59890103</v>
       </c>
       <c r="E6">
-        <v>574185957</v>
+        <v>916682238</v>
       </c>
       <c r="F6">
-        <v>567709101.4791918</v>
+        <v>599193046.1103195</v>
       </c>
       <c r="G6">
-        <v>565706695.8348813</v>
+        <v>592434108.9725909</v>
       </c>
       <c r="H6">
-        <v>406482909.2984353</v>
+        <v>590344494.0613664</v>
+      </c>
+      <c r="I6">
+        <v>424186153.71032864</v>
       </c>
     </row>
     <row r="7">
@@ -3960,10 +4314,16 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>5171537</v>
+        <v>8345843</v>
+      </c>
+      <c r="C7">
+        <v>5396769.061181034</v>
       </c>
       <c r="E7">
-        <v>-34294482</v>
+        <v>-21484934</v>
+      </c>
+      <c r="F7">
+        <v>-35788083.77989558</v>
       </c>
     </row>
     <row r="8">
@@ -3971,35 +4331,38 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>6965013</v>
+        <v>9806264</v>
       </c>
       <c r="C8">
-        <v>7579313.712582651</v>
+        <v>7268354.972443143</v>
       </c>
       <c r="D8">
-        <v>9709188.377610411</v>
+        <v>7909409.861913625</v>
       </c>
       <c r="E8">
-        <v>8530318</v>
+        <v>10132047</v>
       </c>
       <c r="F8">
-        <v>4984777.1576447</v>
+        <v>8901832.523761442</v>
       </c>
       <c r="G8">
-        <v>7432313.295753423</v>
+        <v>5201875.407883353</v>
       </c>
       <c r="H8">
-        <v>14481404.646139897</v>
+        <v>7756007.246496838</v>
+      </c>
+      <c r="I8">
+        <v>15112102.370481169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v xml:space="preserve">    Kar Payı (Geliri) Gideri ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>0</v>
       </c>
     </row>
@@ -4007,10 +4370,10 @@
       <c r="A10" t="str">
         <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan (Gelirler) Giderler ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="E10">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>0</v>
       </c>
     </row>
@@ -4018,10 +4381,10 @@
       <c r="A11" t="str">
         <v xml:space="preserve">    Pazarlıklı Satın Alım Sonucu Oluşan Kazanç ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="E11">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>0</v>
       </c>
     </row>
@@ -4029,10 +4392,10 @@
       <c r="A12" t="str">
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="E12">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>0</v>
       </c>
     </row>
@@ -4040,10 +4403,10 @@
       <c r="A13" t="str">
         <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Gelirler ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="E13">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>0</v>
       </c>
     </row>
@@ -4051,10 +4414,10 @@
       <c r="A14" t="str">
         <v xml:space="preserve">    Takas İşlemlerinden Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="E14">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>0</v>
       </c>
     </row>
@@ -4062,36 +4425,33 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
       <c r="C15">
-        <v>1358290170.6096284</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>605581506.282175</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
+        <v>1417446760.7700284</v>
       </c>
       <c r="F15">
-        <v>189186295.2020995</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>706298747.4301203</v>
+        <v>197425783.62025687</v>
       </c>
       <c r="H15">
-        <v>1127231139.0235205</v>
+        <v>737059645.5331926</v>
+      </c>
+      <c r="I15">
+        <v>1176324588.972677</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v xml:space="preserve">    Pay Bazlı Ödemeler İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="E16">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>0</v>
       </c>
     </row>
@@ -4099,10 +4459,10 @@
       <c r="A17" t="str">
         <v xml:space="preserve">    Hibe Krediler ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="E17">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="F17">
         <v>0</v>
       </c>
     </row>
@@ -4110,36 +4470,33 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
       <c r="C18">
-        <v>-307240006.8954623</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>894056949.0472293</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
+        <v>-320620999.8247094</v>
       </c>
       <c r="F18">
-        <v>22381148.06963862</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>-597476402.6130638</v>
+        <v>23355897.377498668</v>
       </c>
       <c r="H18">
-        <v>-670739251.0277348</v>
+        <v>-623497842.9832225</v>
+      </c>
+      <c r="I18">
+        <v>-699951453.1301271</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Dağıtılmamış Karları ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="E19">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>0</v>
       </c>
     </row>
@@ -4148,46 +4505,49 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>606840759</v>
+        <v>780288440</v>
+      </c>
+      <c r="C20">
+        <v>633270038.140463</v>
       </c>
       <c r="E20">
-        <v>2057820158</v>
+        <v>1139819585</v>
+      </c>
+      <c r="F20">
+        <v>2147442851.548595</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
       <c r="C21">
-        <v>-307240006.8954623</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>894056949.0472293</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
+        <v>-320620999.8247094</v>
       </c>
       <c r="F21">
-        <v>22381148.06963862</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>-597476402.6130638</v>
+        <v>23355897.377498668</v>
       </c>
       <c r="H21">
-        <v>-670739251.0277348</v>
+        <v>-623497842.9832225</v>
+      </c>
+      <c r="I21">
+        <v>-699951453.1301271</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="E22">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="F22">
         <v>0</v>
       </c>
     </row>
@@ -4195,10 +4555,10 @@
       <c r="A23" t="str">
         <v xml:space="preserve">    Satış Amaçlı veya Ortaklara Dağıtılmak Üzere Elde Tutulan Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="E23">
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <v>0</v>
       </c>
     </row>
@@ -4206,10 +4566,10 @@
       <c r="A24" t="str">
         <v xml:space="preserve">    İştirak, İş ortaklığı ve Finansal Yatırımların Elden Çıkarılmasından veya Paylarındaki Değişim Sebebi ile Oluşan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="E24">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="F24">
         <v>0</v>
       </c>
     </row>
@@ -4217,10 +4577,10 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Bağlı Ortaklıkların veya Müşterek Faaliyetlerin Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="E25">
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="F25">
         <v>0</v>
       </c>
     </row>
@@ -4228,10 +4588,10 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım ya da Finansman Faaliyetlerinden Kaynaklanan Nakit Akışlarına Neden Olan Diğer Kalemlere İlişkin Düzeltmeler</v>
       </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="E26">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="F26">
         <v>0</v>
       </c>
     </row>
@@ -4240,10 +4600,16 @@
         <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
       </c>
       <c r="B27">
-        <v>1162131858</v>
+        <v>-609193</v>
+      </c>
+      <c r="C27">
+        <v>1212745312.7121067</v>
       </c>
       <c r="E27">
-        <v>59417487</v>
+        <v>1564951080</v>
+      </c>
+      <c r="F27">
+        <v>62005252.12035151</v>
       </c>
     </row>
     <row r="28">
@@ -4251,25 +4617,28 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-1864265914</v>
+        <v>3302365843</v>
       </c>
       <c r="C28">
-        <v>-2117505408.6491091</v>
+        <v>-1945458885.1418023</v>
       </c>
       <c r="D28">
-        <v>1032668847.3301768</v>
+        <v>-2209727529.0268664</v>
       </c>
       <c r="E28">
-        <v>-2227121070</v>
+        <v>-361424595</v>
       </c>
       <c r="F28">
-        <v>2495166497.4270554</v>
+        <v>-2324117198.8289747</v>
       </c>
       <c r="G28">
-        <v>1990692373.2202148</v>
+        <v>2603836607.145956</v>
       </c>
       <c r="H28">
-        <v>-2923613519.496509</v>
+        <v>2077391500.8485682</v>
+      </c>
+      <c r="I28">
+        <v>-3050943460.1104765</v>
       </c>
     </row>
     <row r="29">
@@ -4277,10 +4646,16 @@
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
       <c r="B29">
-        <v>60375057</v>
+        <v>40020805</v>
+      </c>
+      <c r="C29">
+        <v>63004526.44632367</v>
       </c>
       <c r="E29">
-        <v>812511610</v>
+        <v>344867907</v>
+      </c>
+      <c r="F29">
+        <v>847898317.0184009</v>
       </c>
     </row>
     <row r="30">
@@ -4293,45 +4668,45 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>61071794</v>
+        <v>-987124326</v>
       </c>
       <c r="C31">
-        <v>-432192482.261761</v>
+        <v>63731607.9088328</v>
       </c>
       <c r="D31">
-        <v>-138689531.49732614</v>
+        <v>-451015436.36742896</v>
       </c>
       <c r="E31">
-        <v>-175476333</v>
+        <v>-211323024</v>
       </c>
       <c r="F31">
-        <v>-173750517.180102</v>
+        <v>-183118721.7463397</v>
       </c>
       <c r="G31">
-        <v>-212545257.9780791</v>
+        <v>-181317742.76811287</v>
       </c>
       <c r="H31">
-        <v>-95403299.54835147</v>
+        <v>-221802081.73253688</v>
+      </c>
+      <c r="I31">
+        <v>-99558327.69583388</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
-      <c r="C32">
-        <v>50899071.97811102</v>
-      </c>
       <c r="D32">
-        <v>646484048.9454787</v>
-      </c>
-      <c r="F32">
-        <v>571665622.8744863</v>
+        <v>53115840.97615391</v>
       </c>
       <c r="G32">
-        <v>-414005281.16503257</v>
+        <v>596562945.7683107</v>
       </c>
       <c r="H32">
-        <v>60453407.81883486</v>
+        <v>-432036141.7808676</v>
+      </c>
+      <c r="I32">
+        <v>63086289.61943956</v>
       </c>
     </row>
     <row r="33">
@@ -4339,20 +4714,26 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-5565365</v>
+        <v>-70294411</v>
+      </c>
+      <c r="C33">
+        <v>-5807749.155846663</v>
       </c>
       <c r="E33">
-        <v>8179293</v>
+        <v>1663482</v>
+      </c>
+      <c r="F33">
+        <v>8535519.595960466</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="E34">
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="F34">
         <v>0</v>
       </c>
     </row>
@@ -4366,10 +4747,16 @@
         <v xml:space="preserve">    Türev Varlıklardaki Azalış (Artış)</v>
       </c>
       <c r="B36">
-        <v>843291</v>
+        <v>558992</v>
+      </c>
+      <c r="C36">
+        <v>880018.2186403027</v>
       </c>
       <c r="E36">
-        <v>-661076</v>
+        <v>-745978</v>
+      </c>
+      <c r="F36">
+        <v>-689867.3457986113</v>
       </c>
     </row>
     <row r="37">
@@ -4377,25 +4764,28 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-62371334</v>
+        <v>-68703117</v>
       </c>
       <c r="C37">
-        <v>-20703259.45284579</v>
+        <v>-65087745.79700168</v>
       </c>
       <c r="D37">
-        <v>76551138.69744618</v>
+        <v>-21604932.93980531</v>
       </c>
       <c r="E37">
-        <v>-2139560</v>
+        <v>79885112</v>
       </c>
       <c r="F37">
-        <v>-110739758.5720443</v>
+        <v>-2232742.647406466</v>
       </c>
       <c r="G37">
-        <v>84310353.46790883</v>
+        <v>-115562723.984043</v>
       </c>
       <c r="H37">
-        <v>-139639693.92654294</v>
+        <v>87982258.87832716</v>
+      </c>
+      <c r="I37">
+        <v>-145721316.48590273</v>
       </c>
     </row>
     <row r="38">
@@ -4408,25 +4798,28 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>109090249</v>
+        <v>-195300482</v>
       </c>
       <c r="C39">
-        <v>-50873833.17436154</v>
+        <v>113841374.56228878</v>
       </c>
       <c r="D39">
-        <v>-546857191.4172539</v>
+        <v>-53089502.965768136</v>
       </c>
       <c r="E39">
-        <v>-326480233</v>
+        <v>-570674051</v>
       </c>
       <c r="F39">
-        <v>37086282.23513411</v>
+        <v>-340699181.0252107</v>
       </c>
       <c r="G39">
-        <v>1526321248.2617865</v>
+        <v>38701473.1908134</v>
       </c>
       <c r="H39">
-        <v>-1472928030.5457304</v>
+        <v>1592795969.5623224</v>
+      </c>
+      <c r="I39">
+        <v>-1537077357.1948745</v>
       </c>
     </row>
     <row r="40">
@@ -4434,25 +4827,28 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>182151539</v>
+        <v>731843698</v>
       </c>
       <c r="C40">
-        <v>816207688.4875214</v>
+        <v>190084647.97249067</v>
       </c>
       <c r="D40">
-        <v>192317080.81488553</v>
+        <v>851755368.032278</v>
       </c>
       <c r="E40">
-        <v>6498851</v>
+        <v>263852177</v>
       </c>
       <c r="F40">
-        <v>129539999.10664491</v>
+        <v>6781890.569481649</v>
       </c>
       <c r="G40">
-        <v>-495819589.29256713</v>
+        <v>135181757.2540156</v>
       </c>
       <c r="H40">
-        <v>-359601128.79264534</v>
+        <v>-517413646.9335157</v>
+      </c>
+      <c r="I40">
+        <v>-375262566.28037745</v>
       </c>
     </row>
     <row r="41">
@@ -4465,35 +4861,38 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>6054033</v>
+        <v>-5562259</v>
       </c>
       <c r="C42">
-        <v>7629376.353167293</v>
+        <v>6317699.745698231</v>
       </c>
       <c r="D42">
-        <v>-3402710.421611854</v>
+        <v>7961652.843028954</v>
       </c>
       <c r="E42">
-        <v>7932176</v>
+        <v>-3550907</v>
       </c>
       <c r="F42">
-        <v>12623479.515945815</v>
+        <v>8277640.095128919</v>
       </c>
       <c r="G42">
-        <v>-5438087.659865205</v>
+        <v>13173260.424533151</v>
       </c>
       <c r="H42">
-        <v>2792977.8185283686</v>
+        <v>-5674928.601448836</v>
+      </c>
+      <c r="I42">
+        <v>2914618.2807159256</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="E43">
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="F43">
         <v>0</v>
       </c>
     </row>
@@ -4502,25 +4901,28 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-472592552</v>
+        <v>-306482883</v>
       </c>
       <c r="C44">
-        <v>-298910063.18672997</v>
+        <v>-493175019.9559993</v>
       </c>
       <c r="D44">
-        <v>866505283.1240386</v>
+        <v>-311928268.3430114</v>
       </c>
       <c r="E44">
-        <v>710807180</v>
+        <v>711763293</v>
       </c>
       <c r="F44">
-        <v>37694866.69141841</v>
+        <v>741764430.4757633</v>
       </c>
       <c r="G44">
-        <v>770807543.0491066</v>
+        <v>39336562.868174456</v>
       </c>
       <c r="H44">
-        <v>-390904978.2321905</v>
+        <v>804377944.2073771</v>
+      </c>
+      <c r="I44">
+        <v>-407929768.72932184</v>
       </c>
     </row>
     <row r="45">
@@ -4538,25 +4940,28 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-32924757</v>
+        <v>497635702</v>
       </c>
       <c r="C47">
-        <v>5484117.811083051</v>
+        <v>-34358704.17721147</v>
       </c>
       <c r="D47">
-        <v>94069287.34817715</v>
+        <v>5722963.469221019</v>
       </c>
       <c r="E47">
-        <v>362833804</v>
+        <v>98166216</v>
       </c>
       <c r="F47">
-        <v>807009867.2785577</v>
+        <v>378636031.75957614</v>
       </c>
       <c r="G47">
-        <v>718298179.0594827</v>
+        <v>842156961.0343564</v>
       </c>
       <c r="H47">
-        <v>-17230818.463972263</v>
+        <v>749581679.3829166</v>
+      </c>
+      <c r="I47">
+        <v>-17981259.340345513</v>
       </c>
     </row>
     <row r="48">
@@ -4564,25 +4969,28 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-1710397869</v>
+        <v>3665774124</v>
       </c>
       <c r="C48">
-        <v>-2182446053.670548</v>
+        <v>-1784889540.9100177</v>
       </c>
       <c r="D48">
-        <v>-181138283.8851084</v>
+        <v>-2277496485.115712</v>
       </c>
       <c r="E48">
-        <v>-3631126782</v>
+        <v>-1075328822</v>
       </c>
       <c r="F48">
-        <v>1144167420.2069683</v>
+        <v>-3789270515.578531</v>
       </c>
       <c r="G48">
-        <v>56003859.50245357</v>
+        <v>1193998483.2718563</v>
       </c>
       <c r="H48">
-        <v>-518846172.17053354</v>
+        <v>58442953.47196992</v>
+      </c>
+      <c r="I48">
+        <v>-541443089.2560844</v>
       </c>
     </row>
     <row r="49">
@@ -4590,20 +4998,26 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>3530246236</v>
+        <v>3998368466</v>
+      </c>
+      <c r="C49">
+        <v>3683996395.0360594</v>
       </c>
       <c r="E49">
-        <v>5367805765</v>
+        <v>3544445704</v>
+      </c>
+      <c r="F49">
+        <v>5601585772.079207</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="E50">
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="F50">
         <v>0</v>
       </c>
     </row>
@@ -4611,10 +5025,10 @@
       <c r="A51" t="str">
         <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="E51">
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="F51">
         <v>0</v>
       </c>
     </row>
@@ -4622,10 +5036,10 @@
       <c r="A52" t="str">
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="E52">
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="F52">
         <v>0</v>
       </c>
     </row>
@@ -4633,10 +5047,10 @@
       <c r="A53" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="E53">
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="F53">
         <v>0</v>
       </c>
     </row>
@@ -4644,10 +5058,10 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="E54">
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="F54">
         <v>0</v>
       </c>
     </row>
@@ -4655,10 +5069,10 @@
       <c r="A55" t="str">
         <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="E55">
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="F55">
         <v>0</v>
       </c>
     </row>
@@ -4666,10 +5080,10 @@
       <c r="A56" t="str">
         <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="E56">
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="F56">
         <v>0</v>
       </c>
     </row>
@@ -4677,10 +5091,10 @@
       <c r="A57" t="str">
         <v xml:space="preserve">    Kira Ödemeleri</v>
       </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="E57">
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="F57">
         <v>0</v>
       </c>
     </row>
@@ -4688,10 +5102,10 @@
       <c r="A58" t="str">
         <v xml:space="preserve">    Alınan Kira</v>
       </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-      <c r="E58">
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="F58">
         <v>0</v>
       </c>
     </row>
@@ -4699,10 +5113,10 @@
       <c r="A59" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-      <c r="E59">
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="F59">
         <v>0</v>
       </c>
     </row>
@@ -4710,10 +5124,10 @@
       <c r="A60" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
-      <c r="B60">
-        <v>0</v>
-      </c>
-      <c r="E60">
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="F60">
         <v>0</v>
       </c>
     </row>
@@ -4721,10 +5135,10 @@
       <c r="A61" t="str">
         <v xml:space="preserve">    İştirakler, İş Ortaklıkları ve/veya Müşterek Faaliyetlerin Sermaye Artırımına Katılımdan Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="E61">
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="F61">
         <v>0</v>
       </c>
     </row>
@@ -4732,10 +5146,10 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="B62">
-        <v>0</v>
-      </c>
-      <c r="E62">
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="F62">
         <v>0</v>
       </c>
     </row>
@@ -4743,874 +5157,926 @@
       <c r="A63" t="str">
         <v xml:space="preserve">    Diğer Karşılıklara İlişkin Ödemeler</v>
       </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="E63">
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="F63">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="E64">
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="F64">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
-      <c r="B66">
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67"/>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>222881737</v>
+      </c>
+      <c r="C67">
+        <v>-327682648.0769893</v>
+      </c>
+      <c r="E67">
+        <v>-56864989</v>
+      </c>
+      <c r="F67">
+        <v>-426133968.71475875</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>-314006940</v>
-      </c>
-      <c r="E68">
-        <v>-408349433</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
-      </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="E69">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="F69">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
-      </c>
-      <c r="B70">
-        <v>0</v>
-      </c>
-      <c r="E70">
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="F70">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B71">
-        <v>0</v>
-      </c>
-      <c r="E71">
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="F71">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="E72">
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="F72">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
-      </c>
-      <c r="B73">
-        <v>0</v>
-      </c>
-      <c r="E73">
-        <v>0</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>124109.61421634203</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
-      </c>
-      <c r="B74">
-        <v>0</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>118929.94765929053</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
-      </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="E75">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="F75">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
-      </c>
-      <c r="B76">
-        <v>0</v>
-      </c>
-      <c r="E76">
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="F76">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>183395399</v>
+      </c>
+      <c r="C77">
+        <v>182234231.90631738</v>
+      </c>
+      <c r="D77">
+        <v>119603018.75430453</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>34848719</v>
+      </c>
+      <c r="F77">
+        <v>2119743.6793527002</v>
+      </c>
+      <c r="G77">
+        <v>-322865703.5135353</v>
+      </c>
+      <c r="H77">
+        <v>-10342269972.432505</v>
+      </c>
+      <c r="I77">
+        <v>-1728919485.9789412</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>174628757</v>
+        <v>-207037377</v>
       </c>
       <c r="C78">
-        <v>114611433.20893183</v>
+        <v>-647068995.2575537</v>
       </c>
       <c r="D78">
-        <v>-804348116.8339394</v>
+        <v>-1174319.407819499</v>
       </c>
       <c r="E78">
-        <v>2031277</v>
+        <v>-874133624</v>
       </c>
       <c r="F78">
-        <v>-309391028.74746263</v>
+        <v>-1089220289.8481476</v>
       </c>
       <c r="G78">
-        <v>-9910639351.078491</v>
+        <v>-1617008.219687948</v>
       </c>
       <c r="H78">
-        <v>-1656763702.578072</v>
+        <v>-14752715.355485175</v>
+      </c>
+      <c r="I78">
+        <v>-21059046.0660309</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B79">
-        <v>-620063822</v>
+        <v>13663810</v>
       </c>
       <c r="C79">
-        <v>-1125309.6433271503</v>
-      </c>
-      <c r="D79">
-        <v>-3921399.713712857</v>
+        <v>13663809.796128556</v>
       </c>
       <c r="E79">
-        <v>-1043762104</v>
+        <v>24869363</v>
       </c>
       <c r="F79">
-        <v>-1549523.009530134</v>
-      </c>
-      <c r="G79">
-        <v>-14137016.508663323</v>
-      </c>
-      <c r="H79">
-        <v>-20180154.955778264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B80">
-        <v>13093556</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>-13033026.291498626</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B81">
-        <v>0</v>
-      </c>
-      <c r="E81">
-        <v>-12489098</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B82">
-        <v>0</v>
-      </c>
-      <c r="E82">
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="F82">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
-      </c>
-      <c r="B83">
-        <v>0</v>
-      </c>
-      <c r="E83">
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="F83">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B84">
-        <v>0</v>
-      </c>
-      <c r="E84">
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="F84">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="E85">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="F85">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B86">
-        <v>0</v>
-      </c>
-      <c r="E86">
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="F86">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B87">
-        <v>0</v>
-      </c>
-      <c r="E87">
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="F87">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
-      </c>
-      <c r="B88">
-        <v>0</v>
-      </c>
-      <c r="E88">
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="F88">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
-      </c>
-      <c r="B89">
-        <v>0</v>
-      </c>
-      <c r="E89">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="F89">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
-      </c>
-      <c r="B90">
-        <v>0</v>
-      </c>
-      <c r="E90">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="F90">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
-      </c>
-      <c r="B91">
-        <v>0</v>
-      </c>
-      <c r="E91">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="F91">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
-      </c>
-      <c r="B92">
-        <v>0</v>
-      </c>
-      <c r="E92">
+        <v xml:space="preserve">    Alınan Temettüler</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="F92">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
-      </c>
-      <c r="B93">
-        <v>0</v>
-      </c>
-      <c r="E93">
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="F93">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>232859905</v>
+      </c>
+      <c r="C94">
+        <v>123488305.47811845</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>757550553</v>
+      </c>
+      <c r="F94">
+        <v>673999603.7455349</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B95">
-        <v>118334569</v>
-      </c>
-      <c r="E95">
-        <v>645870492</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-      <c r="B96">
-        <v>0</v>
-      </c>
-      <c r="E96">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="F96">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-      <c r="B97">
-        <v>0</v>
-      </c>
-      <c r="E97">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="F97">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
-      </c>
-      <c r="B98">
-        <v>0</v>
-      </c>
-      <c r="E98">
-        <v>0</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>13663809.093328267</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>-13033027.375241447</v>
+      </c>
+      <c r="H98">
+        <v>-38533172.21623986</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
       <c r="C99">
-        <v>13093555.326530809</v>
-      </c>
-      <c r="D99">
-        <v>23831449.909851637</v>
-      </c>
-      <c r="E99">
         <v>0</v>
       </c>
       <c r="F99">
-        <v>-12489099.038513236</v>
-      </c>
-      <c r="G99">
-        <v>-36925005.23638245</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>-2959433817</v>
+      </c>
+      <c r="C101">
+        <v>-2884596936.0242605</v>
+      </c>
+      <c r="D101">
+        <v>685121109.2460116</v>
+      </c>
+      <c r="E101">
+        <v>-3163483684</v>
+      </c>
+      <c r="F101">
+        <v>-4824759636.975395</v>
+      </c>
+      <c r="G101">
+        <v>-2776774850.82432</v>
+      </c>
+      <c r="H101">
+        <v>3295908919.437393</v>
+      </c>
+      <c r="I101">
+        <v>2694192957.6993012</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>-2764209403</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="C102">
-        <v>656527845.7869401</v>
-      </c>
-      <c r="D102">
-        <v>-3027015340.7196226</v>
-      </c>
-      <c r="E102">
-        <v>-4623400167</v>
+        <v>0</v>
       </c>
       <c r="F102">
-        <v>-2660887230.6581254</v>
-      </c>
-      <c r="G102">
-        <v>3158355440.4995003</v>
-      </c>
-      <c r="H102">
-        <v>2581751860.7757945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-      <c r="E103">
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="F103">
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B104">
-        <v>0</v>
-      </c>
-      <c r="E104">
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="F104">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
       <c r="B105">
+        <v>110000000</v>
+      </c>
+      <c r="C105">
         <v>0</v>
       </c>
       <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
-      </c>
-      <c r="B106">
-        <v>0</v>
-      </c>
-      <c r="E106">
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="F106">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
-      </c>
-      <c r="B107">
-        <v>0</v>
-      </c>
-      <c r="E107">
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="F107">
         <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B108">
-        <v>0</v>
-      </c>
-      <c r="E108">
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="F108">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>3619826626</v>
+      </c>
+      <c r="C109">
+        <v>2028221079.1727893</v>
+      </c>
+      <c r="D109">
+        <v>1794896259.2103815</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>8563301146</v>
+      </c>
+      <c r="F109">
+        <v>2846425847.465238</v>
+      </c>
+      <c r="G109">
+        <v>-1229900182.3181372</v>
+      </c>
+      <c r="H109">
+        <v>3964148428.6754355</v>
+      </c>
+      <c r="I109">
+        <v>4035963452.6487164</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>1943574060</v>
+        <v>-4025822642</v>
       </c>
       <c r="C110">
-        <v>1719986960.7977474</v>
+        <v>-3421310665.099076</v>
       </c>
       <c r="D110">
-        <v>-470963121.65234965</v>
+        <v>-55179231.18529645</v>
       </c>
       <c r="E110">
-        <v>2727631370</v>
+        <v>-8871775223</v>
       </c>
       <c r="F110">
-        <v>-1178570775.7843285</v>
-      </c>
-      <c r="G110">
-        <v>3798706233.29961</v>
+        <v>-4805180897.9027</v>
       </c>
       <c r="H110">
-        <v>3867524085.1334314</v>
+        <v>-234717957.29653564</v>
+      </c>
+      <c r="I110">
+        <v>-310498833.60632724</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B111">
-        <v>-3278523593</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
       <c r="C111">
-        <v>-52876347.398097806</v>
-      </c>
-      <c r="D111">
-        <v>-282169383.0011015</v>
-      </c>
-      <c r="E111">
-        <v>-4604638539</v>
-      </c>
-      <c r="G111">
-        <v>-224922094.49070135</v>
-      </c>
-      <c r="H111">
-        <v>-297540285.353726</v>
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
-      </c>
-      <c r="B112">
-        <v>0</v>
-      </c>
-      <c r="E112">
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="F112">
         <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
-      </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-      <c r="E113">
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="F113">
         <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B114">
-        <v>0</v>
-      </c>
-      <c r="E114">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="F114">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
-      </c>
-      <c r="B115">
-        <v>0</v>
-      </c>
-      <c r="E115">
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="F115">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
-      </c>
-      <c r="B116">
-        <v>0</v>
-      </c>
-      <c r="E116">
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="F116">
         <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
-      </c>
-      <c r="B117">
-        <v>0</v>
-      </c>
-      <c r="E117">
+        <v xml:space="preserve">    Ödenen Temettüler</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="F117">
         <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>-2533703405</v>
+      </c>
+      <c r="C118">
+        <v>-1376835066.8858287</v>
+      </c>
+      <c r="D118">
+        <v>-1054595919.9009377</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>-2372915547</v>
+      </c>
+      <c r="F118">
+        <v>-2436896683.8433156</v>
+      </c>
+      <c r="G118">
+        <v>-1546874668.5061824</v>
+      </c>
+      <c r="H118">
+        <v>-827437879.1734134</v>
+      </c>
+      <c r="I118">
+        <v>-1031271661.343088</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-      <c r="B119">
-        <v>-1319373390</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="C119">
-        <v>-1010582768.6877532</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>-2273882836.066171</v>
-      </c>
-      <c r="E119">
-        <v>-2335193747</v>
+        <v>94559599.49247646</v>
       </c>
       <c r="F119">
-        <v>-1482316454.8737967</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>-792905080.5836018</v>
+        <v>157298916.6483077</v>
       </c>
       <c r="H119">
-        <v>-988231939.003911</v>
+        <v>362929274.89635617</v>
+      </c>
+      <c r="I119">
+        <v>96678760.9462545</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B120">
-        <v>0</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
       <c r="C120">
-        <v>90613191.3255347</v>
-      </c>
-      <c r="D120">
-        <v>725934475.469716</v>
-      </c>
-      <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>150734107.44179913</v>
-      </c>
-      <c r="G120">
-        <v>347782562.535469</v>
-      </c>
-      <c r="H120">
-        <v>92643910.39891832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
-      </c>
-      <c r="B121">
-        <v>0</v>
-      </c>
-      <c r="E121">
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="F121">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
-      </c>
-      <c r="B122">
-        <v>0</v>
-      </c>
-      <c r="E122">
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="F122">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>-129734396</v>
+      </c>
+      <c r="C123">
+        <v>-114672283.21214533</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>-482094060</v>
+      </c>
+      <c r="F123">
+        <v>-429107902.6946175</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="B124">
-        <v>-109886480</v>
-      </c>
-      <c r="E124">
-        <v>-411199251</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>1261816386</v>
+      </c>
+      <c r="C125">
+        <v>471716810.93480974</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>324097031</v>
+      </c>
+      <c r="F125">
+        <v>350692166.3890539</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B126">
-        <v>452029893</v>
-      </c>
-      <c r="E126">
-        <v>336056165</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>1261816386</v>
+      </c>
+      <c r="C127">
+        <v>471716810.93480974</v>
+      </c>
+      <c r="D127">
+        <v>741895503.7075094</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>324097031</v>
+      </c>
+      <c r="F127">
+        <v>350692166.3890539</v>
+      </c>
+      <c r="G127">
+        <v>-7843466.672814694</v>
+      </c>
+      <c r="H127">
+        <v>-504877800.6893687</v>
+      </c>
+      <c r="I127">
+        <v>163174449.18770054</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>452029893</v>
+        <v>430410841</v>
       </c>
       <c r="C128">
-        <v>710932782.9413154</v>
-      </c>
-      <c r="D128">
-        <v>219920199.41031936</v>
+        <v>551604788.6645334</v>
       </c>
       <c r="E128">
-        <v>336056165</v>
+        <v>200912622</v>
       </c>
       <c r="F128">
-        <v>-7516122.636874755</v>
-      </c>
-      <c r="G128">
-        <v>-483806921.72369957</v>
-      </c>
-      <c r="H128">
-        <v>156364426.91215357</v>
+        <v>200912622.27547947</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>528583777</v>
+        <v>1590644550</v>
+      </c>
+      <c r="C129">
+        <v>1023321599.5993431</v>
       </c>
       <c r="E129">
-        <v>192527612</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B130">
-        <v>980613670</v>
-      </c>
-      <c r="E130">
-        <v>528583777</v>
+        <v>430410841</v>
+      </c>
+      <c r="F129">
+        <v>551604788.6645334</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:I129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -5618,6 +6084,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5625,24 +6092,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5656,13 +6126,16 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>3771269774.570665</v>
-      </c>
-      <c r="D3">
-        <v>-2121545268.5352616</v>
+        <v>314372070.9639406</v>
+      </c>
+      <c r="C3">
+        <v>3935517050.495846</v>
       </c>
       <c r="E3">
-        <v>2579916906.12582</v>
+        <v>-2057140068.0792074</v>
+      </c>
+      <c r="F3">
+        <v>2692278086.6496205</v>
       </c>
     </row>
     <row r="4">
@@ -5670,13 +6143,16 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>3584692.3466286957</v>
-      </c>
-      <c r="D4">
-        <v>-21609014.104403734</v>
+        <v>238999496.1940889</v>
+      </c>
+      <c r="C4">
+        <v>3740813.7561692297</v>
       </c>
       <c r="E4">
-        <v>479991516.0878017</v>
+        <v>-22550135.090338707</v>
+      </c>
+      <c r="F4">
+        <v>500896225.5615742</v>
       </c>
     </row>
     <row r="5">
@@ -5684,13 +6160,16 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>3514445587.5749273</v>
-      </c>
-      <c r="D5">
-        <v>-5359726168.535903</v>
+        <v>-5172452153.371951</v>
+      </c>
+      <c r="C5">
+        <v>3667507592.8546133</v>
       </c>
       <c r="E5">
-        <v>6822212956.39003</v>
+        <v>-3997282536.8178434</v>
+      </c>
+      <c r="F5">
+        <v>7119335665.9411125</v>
       </c>
     </row>
     <row r="6">
@@ -5698,32 +6177,44 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>165928541.76140505</v>
-      </c>
-      <c r="D6">
-        <v>313283762.0976033</v>
+        <v>188959565.663782</v>
+      </c>
+      <c r="C6">
+        <v>173155102.73731697</v>
       </c>
       <c r="E6">
-        <v>6476855.52080822</v>
+        <v>317489191.8896805</v>
+      </c>
+      <c r="F6">
+        <v>6758937.137728572</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B7">
+        <v>2949073.938818966</v>
+      </c>
+      <c r="E7">
+        <v>14303149.779895581</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-614300.7125826506</v>
-      </c>
-      <c r="D8">
-        <v>1178870.3776104115</v>
+        <v>2537909.027556857</v>
+      </c>
+      <c r="C8">
+        <v>-641054.8894704822</v>
       </c>
       <c r="E8">
-        <v>3545540.8423552997</v>
+        <v>1230214.476238558</v>
+      </c>
+      <c r="F8">
+        <v>3699957.1158780893</v>
       </c>
     </row>
     <row r="9">
@@ -5760,14 +6251,11 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B15">
-        <v>-1358290170.6096284</v>
-      </c>
-      <c r="D15">
-        <v>605581506.282175</v>
-      </c>
-      <c r="E15">
-        <v>-189186295.2020995</v>
+      <c r="C15">
+        <v>-1417446760.7700284</v>
+      </c>
+      <c r="F15">
+        <v>-197425783.62025687</v>
       </c>
     </row>
     <row r="16">
@@ -5784,14 +6272,11 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B18">
-        <v>307240006.8954623</v>
-      </c>
-      <c r="D18">
-        <v>894056949.0472293</v>
-      </c>
-      <c r="E18">
-        <v>-22381148.06963862</v>
+      <c r="C18">
+        <v>320620999.8247094</v>
+      </c>
+      <c r="F18">
+        <v>-23355897.377498668</v>
       </c>
     </row>
     <row r="19">
@@ -5803,19 +6288,22 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B20">
+        <v>147018401.859537</v>
+      </c>
+      <c r="E20">
+        <v>-1007623266.548595</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="B21">
-        <v>307240006.8954623</v>
-      </c>
-      <c r="D21">
-        <v>894056949.0472293</v>
-      </c>
-      <c r="E21">
-        <v>-22381148.06963862</v>
+      <c r="C21">
+        <v>320620999.8247094</v>
+      </c>
+      <c r="F21">
+        <v>-23355897.377498668</v>
       </c>
     </row>
     <row r="22">
@@ -5847,25 +6335,40 @@
       <c r="A27" t="str">
         <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
       </c>
+      <c r="B27">
+        <v>-1213354505.7121067</v>
+      </c>
+      <c r="E27">
+        <v>1502945827.8796484</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>253239494.64910913</v>
-      </c>
-      <c r="D28">
-        <v>3259789917.330177</v>
+        <v>5247824728.141802</v>
+      </c>
+      <c r="C28">
+        <v>264268643.88506413</v>
       </c>
       <c r="E28">
-        <v>-4722287567.427055</v>
+        <v>1962692603.8289747</v>
+      </c>
+      <c r="F28">
+        <v>-4927953805.974931</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
+      <c r="B29">
+        <v>-22983721.44632367</v>
+      </c>
+      <c r="E29">
+        <v>-503030410.0184009</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -5877,13 +6380,16 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>493264276.261761</v>
-      </c>
-      <c r="D31">
-        <v>36786801.502673864</v>
+        <v>-1050855933.9088328</v>
+      </c>
+      <c r="C31">
+        <v>514747044.27626175</v>
       </c>
       <c r="E31">
-        <v>-1725815.8198980093</v>
+        <v>-28204302.25366029</v>
+      </c>
+      <c r="F31">
+        <v>-1800978.9782268405</v>
       </c>
     </row>
     <row r="32">
@@ -5895,6 +6401,12 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B33">
+        <v>-64486661.84415334</v>
+      </c>
+      <c r="E33">
+        <v>-6872037.595960466</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -5910,19 +6422,28 @@
       <c r="A36" t="str">
         <v xml:space="preserve">    Türev Varlıklardaki Azalış (Artış)</v>
       </c>
+      <c r="B36">
+        <v>-321026.21864030266</v>
+      </c>
+      <c r="E36">
+        <v>-56110.65420138871</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-41668074.54715421</v>
-      </c>
-      <c r="D37">
-        <v>78690698.69744618</v>
+        <v>-3615371.202998318</v>
+      </c>
+      <c r="C37">
+        <v>-43482812.857196376</v>
       </c>
       <c r="E37">
-        <v>108600198.5720443</v>
+        <v>82117854.64740646</v>
+      </c>
+      <c r="F37">
+        <v>113329981.33663654</v>
       </c>
     </row>
     <row r="38">
@@ -5935,13 +6456,16 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>159964082.17436153</v>
-      </c>
-      <c r="D39">
-        <v>-220376958.41725385</v>
+        <v>-309141856.56228876</v>
+      </c>
+      <c r="C39">
+        <v>166930877.52805692</v>
       </c>
       <c r="E39">
-        <v>-363566515.2351341</v>
+        <v>-229974869.97478932</v>
+      </c>
+      <c r="F39">
+        <v>-379400654.2160241</v>
       </c>
     </row>
     <row r="40">
@@ -5949,13 +6473,16 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-634056149.4875214</v>
-      </c>
-      <c r="D40">
-        <v>185818229.81488553</v>
+        <v>541759050.0275093</v>
+      </c>
+      <c r="C40">
+        <v>-661670720.0597873</v>
       </c>
       <c r="E40">
-        <v>-123041148.10664491</v>
+        <v>257070286.43051836</v>
+      </c>
+      <c r="F40">
+        <v>-128399866.68453394</v>
       </c>
     </row>
     <row r="41">
@@ -5968,13 +6495,16 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-1575343.3531672927</v>
-      </c>
-      <c r="D42">
-        <v>-11334886.421611853</v>
+        <v>-11879958.745698232</v>
+      </c>
+      <c r="C42">
+        <v>-1643953.097330723</v>
       </c>
       <c r="E42">
-        <v>-4691303.515945815</v>
+        <v>-11828547.09512892</v>
+      </c>
+      <c r="F42">
+        <v>-4895620.329404232</v>
       </c>
     </row>
     <row r="43">
@@ -5987,13 +6517,16 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-173682488.81327003</v>
-      </c>
-      <c r="D44">
-        <v>155698103.12403858</v>
+        <v>186692136.9559993</v>
+      </c>
+      <c r="C44">
+        <v>-181246751.61298794</v>
       </c>
       <c r="E44">
-        <v>673112313.3085816</v>
+        <v>-30001137.47576332</v>
+      </c>
+      <c r="F44">
+        <v>702427867.6075889</v>
       </c>
     </row>
     <row r="45">
@@ -6011,13 +6544,16 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-38408874.81108305</v>
-      </c>
-      <c r="D47">
-        <v>-268764516.65182287</v>
+        <v>531994406.17721146</v>
+      </c>
+      <c r="C47">
+        <v>-40081667.64643249</v>
       </c>
       <c r="E47">
-        <v>-444176063.27855766</v>
+        <v>-280469815.75957614</v>
+      </c>
+      <c r="F47">
+        <v>-463520929.2747802</v>
       </c>
     </row>
     <row r="48">
@@ -6025,19 +6561,28 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>472048184.67054796</v>
-      </c>
-      <c r="D48">
-        <v>3449988498.1148915</v>
+        <v>5450663664.910018</v>
+      </c>
+      <c r="C48">
+        <v>492606944.20569444</v>
       </c>
       <c r="E48">
-        <v>-4775294202.206968</v>
+        <v>2713941693.578531</v>
+      </c>
+      <c r="F48">
+        <v>-4983268998.850388</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>314372070.9639406</v>
+      </c>
+      <c r="E49">
+        <v>-2057140068.0792074</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -6111,421 +6656,479 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>550564385.0769893</v>
+      </c>
+      <c r="E67">
+        <v>369268979.71475875</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B77">
+        <v>1161167.093682617</v>
+      </c>
+      <c r="C77">
+        <v>62631213.152012855</v>
+      </c>
+      <c r="E77">
+        <v>32728975.3206473</v>
+      </c>
+      <c r="F77">
+        <v>324985447.192888</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>60017323.79106817</v>
-      </c>
-      <c r="D78">
-        <v>-806379393.8339394</v>
+        <v>440031618.2575537</v>
+      </c>
+      <c r="C78">
+        <v>-645894675.8497342</v>
       </c>
       <c r="E78">
-        <v>311422305.74746263</v>
+        <v>215086665.84814763</v>
+      </c>
+      <c r="F78">
+        <v>-1087603281.6284597</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B79">
-        <v>-618938512.3566729</v>
-      </c>
-      <c r="D79">
-        <v>1039840704.2862872</v>
+        <v>0.2038714438676834</v>
       </c>
       <c r="E79">
-        <v>-1042212580.9904698</v>
+        <v>24869363</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+      <c r="B94">
+        <v>109371599.52188155</v>
+      </c>
+      <c r="E94">
+        <v>83550949.2544651</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="C98">
+        <v>-13663809.093328267</v>
+      </c>
+      <c r="F98">
+        <v>13033027.375241447</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="B99">
-        <v>-13093555.326530809</v>
-      </c>
-      <c r="D99">
-        <v>23831449.909851637</v>
-      </c>
-      <c r="E99">
-        <v>12489099.038513236</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>-74836880.97573948</v>
+      </c>
+      <c r="C101">
+        <v>-3569718045.2702723</v>
+      </c>
+      <c r="E101">
+        <v>1661275952.9753952</v>
+      </c>
+      <c r="F101">
+        <v>-2047984786.1510754</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>-3420737248.78694</v>
-      </c>
-      <c r="D102">
-        <v>1596384826.2803774</v>
-      </c>
-      <c r="E102">
-        <v>-1962512936.3418746</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+      </c>
+      <c r="B105">
+        <v>110000000</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B109">
+        <v>1591605546.8272107</v>
+      </c>
+      <c r="C109">
+        <v>233324819.96240783</v>
+      </c>
+      <c r="E109">
+        <v>5716875298.534761</v>
+      </c>
+      <c r="F109">
+        <v>4076326029.7833753</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>223587099.20225263</v>
-      </c>
-      <c r="D110">
-        <v>-3198594491.6523495</v>
+        <v>-604511976.9009242</v>
+      </c>
+      <c r="C110">
+        <v>-3366131433.9137793</v>
       </c>
       <c r="E110">
-        <v>3906202145.7843285</v>
+        <v>-4066594325.0972996</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B111">
-        <v>-3225647245.601902</v>
-      </c>
-      <c r="D111">
-        <v>4322469155.9988985</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="B118">
+        <v>-1156868338.1141713</v>
+      </c>
+      <c r="C118">
+        <v>-322239146.98489106</v>
+      </c>
+      <c r="E118">
+        <v>63981136.8433156</v>
+      </c>
+      <c r="F118">
+        <v>-890022015.3371332</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-      <c r="B119">
-        <v>-308790621.3122468</v>
-      </c>
-      <c r="D119">
-        <v>61310910.93382883</v>
-      </c>
-      <c r="E119">
-        <v>-852877292.1262033</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+      <c r="C119">
+        <v>-94559599.49247646</v>
+      </c>
+      <c r="F119">
+        <v>-157298916.6483077</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B120">
-        <v>-90613191.3255347</v>
-      </c>
-      <c r="D120">
-        <v>725934475.469716</v>
-      </c>
-      <c r="E120">
-        <v>-150734107.44179913</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="B123">
+        <v>-15062112.787854671</v>
+      </c>
+      <c r="E123">
+        <v>-52986157.30538249</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>790099575.0651903</v>
+      </c>
+      <c r="E125">
+        <v>-26595135.38905388</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>790099575.0651903</v>
+      </c>
+      <c r="C127">
+        <v>-270178692.77269965</v>
+      </c>
+      <c r="E127">
+        <v>-26595135.38905388</v>
+      </c>
+      <c r="F127">
+        <v>358535633.06186855</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>-258902889.9413154</v>
-      </c>
-      <c r="D128">
-        <v>-116135965.58968064</v>
+        <v>-121193947.66453338</v>
       </c>
       <c r="E128">
-        <v>343572287.63687474</v>
+        <v>-0.2754794657230377</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>567322950.4006569</v>
+      </c>
+      <c r="E129">
+        <v>-121193947.66453338</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:I129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -6533,6 +7136,7 @@
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6540,24 +7144,27 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6571,19 +7178,22 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>1408700967.4647384</v>
+        <v>3998368466</v>
       </c>
       <c r="C3">
-        <v>217348099.01989347</v>
+        <v>1626856326.956852</v>
       </c>
       <c r="D3">
-        <v>3246260496.4647384</v>
-      </c>
-      <c r="G3">
-        <v>5705321272.024916</v>
+        <v>383617363.11062646</v>
+      </c>
+      <c r="E3">
+        <v>3544445704</v>
       </c>
       <c r="H3">
-        <v>-1385426114.937746</v>
+        <v>5953800838.118742</v>
+      </c>
+      <c r="I3">
+        <v>-1445764536.471124</v>
       </c>
     </row>
     <row r="4">
@@ -6591,19 +7201,22 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>181923001.89559627</v>
+        <v>451395789</v>
       </c>
       <c r="C4">
-        <v>658329825.6367693</v>
+        <v>189846157.7155724</v>
       </c>
       <c r="D4">
-        <v>1267017310.8955963</v>
-      </c>
-      <c r="G4">
-        <v>2201582135.7442603</v>
+        <v>687001569.5209774</v>
+      </c>
+      <c r="E4">
+        <v>1322198763</v>
       </c>
       <c r="H4">
-        <v>149414234.21793836</v>
+        <v>2297465986.578746</v>
+      </c>
+      <c r="I4">
+        <v>155921559.97867292</v>
       </c>
     </row>
     <row r="5">
@@ -6611,19 +7224,22 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-168746034.53590298</v>
+        <v>244606834</v>
       </c>
       <c r="C5">
-        <v>3139021334.2791996</v>
+        <v>1419776450.5541077</v>
       </c>
       <c r="D5">
-        <v>946574341.4640968</v>
-      </c>
-      <c r="G5">
-        <v>1513046764.1354845</v>
+        <v>4871604523.640607</v>
+      </c>
+      <c r="E5">
+        <v>2583671536</v>
       </c>
       <c r="H5">
-        <v>1388773171.4158683</v>
+        <v>1578943351.8132925</v>
+      </c>
+      <c r="I5">
+        <v>1449257364.7825437</v>
       </c>
     </row>
     <row r="6">
@@ -6631,44 +7247,59 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>816951550.0976033</v>
+        <v>714563218</v>
       </c>
       <c r="C6">
-        <v>657499863.8570065</v>
+        <v>843092844.2258985</v>
       </c>
       <c r="D6">
-        <v>887469719.0976033</v>
-      </c>
-      <c r="G6">
-        <v>565706695.8348813</v>
+        <v>676696678.6263101</v>
+      </c>
+      <c r="E6">
+        <v>916682238</v>
       </c>
       <c r="H6">
-        <v>406482909.2984353</v>
+        <v>590344494.0613664</v>
+      </c>
+      <c r="I6">
+        <v>424186153.71032864</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B7">
+        <v>8345843</v>
+      </c>
+      <c r="C7">
+        <v>19699918.841076616</v>
+      </c>
+      <c r="E7">
+        <v>-21484934</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>8143883.3776104115</v>
+        <v>9806264</v>
       </c>
       <c r="C8">
-        <v>12303724.932548363</v>
+        <v>8498569.448681701</v>
       </c>
       <c r="D8">
-        <v>9709188.377610411</v>
-      </c>
-      <c r="G8">
-        <v>7432313.295753423</v>
+        <v>12839581.454030272</v>
+      </c>
+      <c r="E8">
+        <v>10132047</v>
       </c>
       <c r="H8">
-        <v>14481404.646139897</v>
+        <v>7756007.246496838</v>
+      </c>
+      <c r="I8">
+        <v>15112102.370481169</v>
       </c>
     </row>
     <row r="9">
@@ -6705,20 +7336,11 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Gerçekleşmemiş Yabancı Para Çevrim Farkları İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B15">
-        <v>605581506.282175</v>
-      </c>
-      <c r="C15">
-        <v>1774685381.689704</v>
-      </c>
-      <c r="D15">
-        <v>605581506.282175</v>
-      </c>
-      <c r="G15">
-        <v>706298747.4301203</v>
-      </c>
       <c r="H15">
-        <v>1127231139.0235205</v>
+        <v>737059645.5331926</v>
+      </c>
+      <c r="I15">
+        <v>1176324588.972677</v>
       </c>
     </row>
     <row r="16">
@@ -6735,20 +7357,11 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B18">
-        <v>894056949.0472293</v>
-      </c>
-      <c r="C18">
-        <v>564435794.0821284</v>
-      </c>
-      <c r="D18">
-        <v>894056949.0472293</v>
-      </c>
-      <c r="G18">
-        <v>-597476402.6130638</v>
-      </c>
       <c r="H18">
-        <v>-670739251.0277348</v>
+        <v>-623497842.9832225</v>
+      </c>
+      <c r="I18">
+        <v>-699951453.1301271</v>
       </c>
     </row>
     <row r="19">
@@ -6760,25 +7373,25 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B20">
+        <v>780288440</v>
+      </c>
+      <c r="C20">
+        <v>-374353228.40813196</v>
+      </c>
+      <c r="E20">
+        <v>1139819585</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="B21">
-        <v>894056949.0472293</v>
-      </c>
-      <c r="C21">
-        <v>564435794.0821284</v>
-      </c>
-      <c r="D21">
-        <v>894056949.0472293</v>
-      </c>
-      <c r="G21">
-        <v>-597476402.6130638</v>
-      </c>
       <c r="H21">
-        <v>-670739251.0277348</v>
+        <v>-623497842.9832225</v>
+      </c>
+      <c r="I21">
+        <v>-699951453.1301271</v>
       </c>
     </row>
     <row r="22">
@@ -6810,31 +7423,52 @@
       <c r="A27" t="str">
         <v xml:space="preserve">    Kar (Zarar) Mutabakatı İle İlgili Diğer Düzeltmeler</v>
       </c>
+      <c r="B27">
+        <v>-609193</v>
+      </c>
+      <c r="C27">
+        <v>2715691140.591755</v>
+      </c>
+      <c r="E27">
+        <v>1564951080</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>1395524003.3301768</v>
+        <v>3302365843</v>
       </c>
       <c r="C28">
-        <v>-3580003058.745988</v>
+        <v>17233718.687172413</v>
       </c>
       <c r="D28">
-        <v>1032668847.3301768</v>
-      </c>
-      <c r="G28">
-        <v>1990692373.2202148</v>
+        <v>-5174988731.172823</v>
+      </c>
+      <c r="E28">
+        <v>-361424595</v>
       </c>
       <c r="H28">
-        <v>-2923613519.496509</v>
+        <v>2077391500.8485682</v>
+      </c>
+      <c r="I28">
+        <v>-3050943460.1104765</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
+      <c r="B29">
+        <v>40020805</v>
+      </c>
+      <c r="C29">
+        <v>-440025883.5720772</v>
+      </c>
+      <c r="E29">
+        <v>344867907</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -6846,42 +7480,48 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>97858595.50267386</v>
+        <v>-987124326</v>
       </c>
       <c r="C31">
-        <v>-397131496.57898515</v>
+        <v>35527305.65517251</v>
       </c>
       <c r="D31">
-        <v>-138689531.49732614</v>
-      </c>
-      <c r="G31">
-        <v>-212545257.9780791</v>
+        <v>-481020717.5993161</v>
+      </c>
+      <c r="E31">
+        <v>-211323024</v>
       </c>
       <c r="H31">
-        <v>-95403299.54835147</v>
+        <v>-221802081.73253688</v>
+      </c>
+      <c r="I31">
+        <v>-99558327.69583388</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
-      <c r="C32">
-        <v>125717498.04910338</v>
-      </c>
-      <c r="D32">
-        <v>646484048.9454787</v>
-      </c>
-      <c r="G32">
-        <v>-414005281.16503257</v>
-      </c>
       <c r="H32">
-        <v>60453407.81883486</v>
+        <v>-432036141.7808676</v>
+      </c>
+      <c r="I32">
+        <v>63086289.61943956</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B33">
+        <v>-70294411</v>
+      </c>
+      <c r="C33">
+        <v>-12679786.751807129</v>
+      </c>
+      <c r="E33">
+        <v>1663482</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -6897,25 +7537,37 @@
       <c r="A36" t="str">
         <v xml:space="preserve">    Türev Varlıklardaki Azalış (Artış)</v>
       </c>
+      <c r="B36">
+        <v>558992</v>
+      </c>
+      <c r="C36">
+        <v>823907.564438914</v>
+      </c>
+      <c r="E36">
+        <v>-745978</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>16319364.697446182</v>
+        <v>-68703117</v>
       </c>
       <c r="C37">
-        <v>166587637.8166447</v>
+        <v>17030108.850404777</v>
       </c>
       <c r="D37">
-        <v>76551138.69744618</v>
-      </c>
-      <c r="G37">
-        <v>84310353.46790883</v>
+        <v>173842903.0442377</v>
+      </c>
+      <c r="E37">
+        <v>79885112</v>
       </c>
       <c r="H37">
-        <v>-139639693.92654294</v>
+        <v>87982258.87832716</v>
+      </c>
+      <c r="I37">
+        <v>-145721316.48590273</v>
       </c>
     </row>
     <row r="38">
@@ -6928,19 +7580,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-111286709.41725385</v>
+        <v>-195300482</v>
       </c>
       <c r="C39">
-        <v>-634817306.8267496</v>
+        <v>-116133495.41250055</v>
       </c>
       <c r="D39">
-        <v>-546857191.4172539</v>
-      </c>
-      <c r="G39">
-        <v>1526321248.2617865</v>
+        <v>-662465027.1565815</v>
+      </c>
+      <c r="E39">
+        <v>-570674051</v>
       </c>
       <c r="H39">
-        <v>-1472928030.5457304</v>
+        <v>1592795969.5623224</v>
+      </c>
+      <c r="I39">
+        <v>-1537077357.1948745</v>
       </c>
     </row>
     <row r="40">
@@ -6948,19 +7603,22 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>367969768.8148855</v>
+        <v>731843698</v>
       </c>
       <c r="C40">
-        <v>878984770.195762</v>
+        <v>447154934.40300906</v>
       </c>
       <c r="D40">
-        <v>192317080.81488553</v>
-      </c>
-      <c r="G40">
-        <v>-495819589.29256713</v>
+        <v>980425787.7782624</v>
+      </c>
+      <c r="E40">
+        <v>263852177</v>
       </c>
       <c r="H40">
-        <v>-359601128.79264534</v>
+        <v>-517413646.9335157</v>
+      </c>
+      <c r="I40">
+        <v>-375262566.28037745</v>
       </c>
     </row>
     <row r="41">
@@ -6973,19 +7631,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-5280853.421611853</v>
+        <v>-5562259</v>
       </c>
       <c r="C42">
-        <v>-8396813.584390376</v>
+        <v>-5510847.349430689</v>
       </c>
       <c r="D42">
-        <v>-3402710.421611854</v>
-      </c>
-      <c r="G42">
-        <v>-5438087.659865205</v>
+        <v>-8762514.581504196</v>
+      </c>
+      <c r="E42">
+        <v>-3550907</v>
       </c>
       <c r="H42">
-        <v>2792977.8185283686</v>
+        <v>-5674928.601448836</v>
+      </c>
+      <c r="I42">
+        <v>2914618.2807159256</v>
       </c>
     </row>
     <row r="43">
@@ -6998,19 +7659,22 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-316894448.8759614</v>
+        <v>-306482883</v>
       </c>
       <c r="C44">
-        <v>529900353.2458902</v>
+        <v>-523176157.43176264</v>
       </c>
       <c r="D44">
-        <v>866505283.1240386</v>
-      </c>
-      <c r="G44">
-        <v>770807543.0491066</v>
+        <v>360498461.7888142</v>
+      </c>
+      <c r="E44">
+        <v>711763293</v>
       </c>
       <c r="H44">
-        <v>-390904978.2321905</v>
+        <v>804377944.2073771</v>
+      </c>
+      <c r="I44">
+        <v>-407929768.72932184</v>
       </c>
     </row>
     <row r="45">
@@ -7028,19 +7692,22 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>-301689273.65182287</v>
+        <v>497635702</v>
       </c>
       <c r="C47">
-        <v>-707456462.1192974</v>
+        <v>-314828519.9367876</v>
       </c>
       <c r="D47">
-        <v>94069287.34817715</v>
-      </c>
-      <c r="G47">
-        <v>718298179.0594827</v>
+        <v>-738267781.5651354</v>
+      </c>
+      <c r="E47">
+        <v>98166216</v>
       </c>
       <c r="H47">
-        <v>-17230818.463972263</v>
+        <v>749581679.3829166</v>
+      </c>
+      <c r="I47">
+        <v>-17981259.340345513</v>
       </c>
     </row>
     <row r="48">
@@ -7048,25 +7715,37 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>1739590629.1148915</v>
+        <v>3665774124</v>
       </c>
       <c r="C48">
-        <v>-3507751757.7626247</v>
+        <v>929052152.6685131</v>
       </c>
       <c r="D48">
-        <v>-181138283.8851084</v>
-      </c>
-      <c r="G48">
-        <v>56003859.50245357</v>
+        <v>-4546823790.387568</v>
+      </c>
+      <c r="E48">
+        <v>-1075328822</v>
       </c>
       <c r="H48">
-        <v>-518846172.17053354</v>
+        <v>58442953.47196992</v>
+      </c>
+      <c r="I48">
+        <v>-541443089.2560844</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>3998368466</v>
+      </c>
+      <c r="C49">
+        <v>1626856326.956852</v>
+      </c>
+      <c r="E49">
+        <v>3544445704</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -7140,466 +7819,536 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>222881737</v>
+      </c>
+      <c r="C67">
+        <v>41586331.63776946</v>
+      </c>
+      <c r="E67">
+        <v>-56864989</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+      </c>
+      <c r="I73">
+        <v>124109.61421634203</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
-      </c>
-      <c r="H74">
-        <v>118929.94765929053</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B77">
+        <v>183395399</v>
+      </c>
+      <c r="C77">
+        <v>214963207.22696468</v>
+      </c>
+      <c r="D77">
+        <v>477317441.26783985</v>
+      </c>
+      <c r="E77">
+        <v>34848719</v>
+      </c>
+      <c r="H77">
+        <v>-10342269972.432505</v>
+      </c>
+      <c r="I77">
+        <v>-1728919485.9789412</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-631750636.8339394</v>
+        <v>-207037377</v>
       </c>
       <c r="C78">
-        <v>-380345654.877545</v>
+        <v>-431982329.40940607</v>
       </c>
       <c r="D78">
-        <v>-804348116.8339394</v>
-      </c>
-      <c r="G78">
-        <v>-9910639351.078491</v>
+        <v>-873690935.1881316</v>
+      </c>
+      <c r="E78">
+        <v>-874133624</v>
       </c>
       <c r="H78">
-        <v>-1656763702.578072</v>
+        <v>-14752715.355485175</v>
+      </c>
+      <c r="I78">
+        <v>-21059046.0660309</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B79">
-        <v>419776882.2862872</v>
+        <v>13663810</v>
       </c>
       <c r="C79">
-        <v>-3497186.347509873</v>
-      </c>
-      <c r="D79">
-        <v>-3921399.713712857</v>
-      </c>
-      <c r="G79">
-        <v>-14137016.508663323</v>
-      </c>
-      <c r="H79">
-        <v>-20180154.955778264</v>
+        <v>38533172.796128556</v>
+      </c>
+      <c r="E79">
+        <v>24869363</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
+      </c>
+      <c r="B94">
+        <v>232859905</v>
+      </c>
+      <c r="C94">
+        <v>207039254.73258355</v>
+      </c>
+      <c r="E94">
+        <v>757550553</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="H98">
+        <v>-38533172.21623986</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="B99">
-        <v>23831449.909851637</v>
-      </c>
-      <c r="C99">
-        <v>49414104.274895675</v>
-      </c>
-      <c r="D99">
-        <v>23831449.909851637</v>
-      </c>
-      <c r="G99">
-        <v>-36925005.23638245</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>-2959433817</v>
+      </c>
+      <c r="C101">
+        <v>-1223320983.0488653</v>
+      </c>
+      <c r="D101">
+        <v>298412276.07033145</v>
+      </c>
+      <c r="E101">
+        <v>-3163483684</v>
+      </c>
+      <c r="H101">
+        <v>3295908919.437393</v>
+      </c>
+      <c r="I101">
+        <v>2694192957.6993012</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>-1167824576.7196226</v>
-      </c>
-      <c r="C102">
-        <v>290399735.7254429</v>
-      </c>
-      <c r="D102">
-        <v>-3027015340.7196226</v>
-      </c>
-      <c r="G102">
-        <v>3158355440.4995003</v>
-      </c>
-      <c r="H102">
-        <v>2581751860.7757945</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+      </c>
+      <c r="B105">
+        <v>110000000</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B109">
+        <v>3619826626</v>
+      </c>
+      <c r="C109">
+        <v>7745096377.707551</v>
+      </c>
+      <c r="D109">
+        <v>11588097587.528519</v>
+      </c>
+      <c r="E109">
+        <v>8563301146</v>
+      </c>
+      <c r="H109">
+        <v>3964148428.6754355</v>
+      </c>
+      <c r="I109">
+        <v>4035963452.6487164</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-1255020431.6523495</v>
+        <v>-4025822642</v>
       </c>
       <c r="C110">
-        <v>2427594614.929726</v>
-      </c>
-      <c r="D110">
-        <v>-470963121.65234965</v>
-      </c>
-      <c r="G110">
-        <v>3798706233.29961</v>
+        <v>-7487904990.196375</v>
+      </c>
+      <c r="E110">
+        <v>-8871775223</v>
       </c>
       <c r="H110">
-        <v>3867524085.1334314</v>
+        <v>-234717957.29653564</v>
+      </c>
+      <c r="I110">
+        <v>-310498833.60632724</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B111">
-        <v>1043945562.9988985</v>
-      </c>
-      <c r="D111">
-        <v>-282169383.0011015</v>
-      </c>
-      <c r="G111">
-        <v>-224922094.49070135</v>
-      </c>
-      <c r="H111">
-        <v>-297540285.353726</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
+      </c>
+      <c r="B118">
+        <v>-2533703405</v>
+      </c>
+      <c r="C118">
+        <v>-1312853930.0425131</v>
+      </c>
+      <c r="D118">
+        <v>-1880636798.3947554</v>
+      </c>
+      <c r="E118">
+        <v>-2372915547</v>
+      </c>
+      <c r="H118">
+        <v>-827437879.1734134</v>
+      </c>
+      <c r="I118">
+        <v>-1031271661.343088</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
-      </c>
-      <c r="B119">
-        <v>-1258062479.0661712</v>
-      </c>
-      <c r="C119">
-        <v>-1802149149.8801277</v>
-      </c>
-      <c r="D119">
-        <v>-2273882836.066171</v>
-      </c>
-      <c r="G119">
-        <v>-792905080.5836018</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="H119">
-        <v>-988231939.003911</v>
+        <v>362929274.89635617</v>
+      </c>
+      <c r="I119">
+        <v>96678760.9462545</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
-      </c>
-      <c r="B120">
-        <v>725934475.469716</v>
-      </c>
-      <c r="C120">
-        <v>665813559.3534515</v>
-      </c>
-      <c r="D120">
-        <v>725934475.469716</v>
-      </c>
-      <c r="G120">
-        <v>347782562.535469</v>
-      </c>
-      <c r="H120">
-        <v>92643910.39891832</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="B123">
+        <v>-129734396</v>
+      </c>
+      <c r="C123">
+        <v>-167658440.51752782</v>
+      </c>
+      <c r="E123">
+        <v>-482094060</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>1261816386</v>
+      </c>
+      <c r="C125">
+        <v>445121675.54575586</v>
+      </c>
+      <c r="E125">
+        <v>324097031</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>1261816386</v>
+      </c>
+      <c r="C127">
+        <v>445121675.54575586</v>
+      </c>
+      <c r="D127">
+        <v>1073836001.3803241</v>
+      </c>
+      <c r="E127">
+        <v>324097031</v>
+      </c>
+      <c r="H127">
+        <v>-504877800.6893687</v>
+      </c>
+      <c r="I127">
+        <v>163174449.18770054</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>335893927.4103193</v>
+        <v>430410841</v>
       </c>
       <c r="C128">
-        <v>938369104.9885095</v>
-      </c>
-      <c r="D128">
-        <v>219920199.41031936</v>
-      </c>
-      <c r="G128">
-        <v>-483806921.72369957</v>
-      </c>
-      <c r="H128">
-        <v>156364426.91215357</v>
+        <v>551604788.389054</v>
+      </c>
+      <c r="E128">
+        <v>200912622</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
+      </c>
+      <c r="B129">
+        <v>1590644550</v>
+      </c>
+      <c r="C129">
+        <v>902127651.9348097</v>
+      </c>
+      <c r="E129">
+        <v>430410841</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
   </ignoredErrors>
 </worksheet>
 </file>